--- a/workbooks/04 Formulas 2 - Logic.xlsx
+++ b/workbooks/04 Formulas 2 - Logic.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="698">
   <si>
     <t>Challenge</t>
   </si>
@@ -2317,6 +2317,27 @@
   </si>
   <si>
     <t>Boss F8</t>
+  </si>
+  <si>
+    <t>COUNT plus one letter.</t>
+  </si>
+  <si>
+    <t>=COUNTA</t>
+  </si>
+  <si>
+    <t>=COUNTA(</t>
+  </si>
+  <si>
+    <t>=COUNTA()</t>
+  </si>
+  <si>
+    <t>COUNTA</t>
+  </si>
+  <si>
+    <t>COUNTA(</t>
+  </si>
+  <si>
+    <t>COUNTA()</t>
   </si>
   <si>
     <t>F8</t>
@@ -3329,7 +3350,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3339,12 +3360,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3354,32 +3375,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3389,7 +3410,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
@@ -3398,21 +3419,21 @@
         <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>558</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F2-1 True or False'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3427,15 +3448,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F2-2 Fork in the Road'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3450,15 +3471,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F2-3 Combo Moves'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3473,15 +3494,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F2-4 Multi-Level'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3496,15 +3517,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM('F2-5 Error Shield'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3519,15 +3540,15 @@
         <v>NEW</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="C18" s="9" cm="1" t="str">
         <f t="array" ref="C18">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3542,12 +3563,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">(SUM('F2-1 True or False'!$G$13:$G$38)+SUM('F2-2 Fork in the Road'!$G$13:$G$38)+SUM('F2-3 Combo Moves'!$G$13:$G$38)+SUM('F2-4 Multi-Level'!$G$13:$G$38)+SUM('F2-5 Error Shield'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 1140"</f>
@@ -3556,19 +3577,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">_xlfn.LET(_xlpm.p,(SUM('F2-1 True or False'!$G$13:$G$38)+SUM('F2-2 Fork in the Road'!$G$13:$G$38)+SUM('F2-3 Combo Moves'!$G$13:$G$38)+SUM('F2-4 Multi-Level'!$G$13:$G$38)+SUM('F2-5 Error Shield'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))/1140,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3577,7 +3598,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="7" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B23" s="12" cm="1" t="str">
         <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3586,7 +3607,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="13" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -4671,7 +4692,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4682,7 +4703,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -4949,10 +4970,10 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B21" s="31" cm="1" t="str">
-        <f t="array" ref="B21">IF($C$10="OPEN","Which function is TRUE only when all its conditions are TRUE?  (from F2-3 Combo Moves)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B21">IF($C$10="OPEN","Which function counts every non-empty cell?  (from F1-2 Big Six)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C21" s="20"/>
@@ -4972,7 +4993,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -4983,7 +5004,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5011,14 +5032,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="B26" s="31" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In F6 return ""Pass"" for a Score of 60 or more, otherwise ""Fail"". Fill down to F15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$F$6,'Boss Arena'!$F$7,'Boss Arena'!$F$8,'Boss Arena'!$F$9,'Boss Arena'!$F$10,'Boss Arena'!$F$11,'Boss Arena'!$F$12,'Boss Arena'!$F$13,'Boss Arena'!$F$14,'Boss Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$F$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$F$6),ISERROR('Boss Arena'!$F$7),ISERROR('Boss Arena'!$F$8),ISERROR('Boss Arena'!$F$9),ISERROR('Boss Arena'!$F$10),ISERROR('Boss Arena'!$F$11),ISERROR('Boss Arena'!$F$12),ISERROR('Boss Arena'!$F$13),ISERROR('Boss Arena'!$F$14),ISERROR('Boss Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$F$6),'Boss Arena'!$F$6=Key!$E$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$7),'Boss Arena'!$F$7=Key!$F$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$8),'Boss Arena'!$F$8=Key!$G$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$9),'Boss Arena'!$F$9=Key!$H$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$10),'Boss Arena'!$F$10=Key!$I$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$11),'Boss Arena'!$F$11=Key!$J$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$12),'Boss Arena'!$F$12=Key!$K$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$13),'Boss Arena'!$F$13=Key!$L$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$14),'Boss Arena'!$F$14=Key!$M$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$15),'Boss Arena'!$F$15=Key!$N$108),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$F$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF"))))),"LOCKED")</f>
@@ -5036,14 +5057,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B27" s="31" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In G6 return ""Yes"" when Age is 18+ AND Score is 70+, otherwise ""No"". Fill down to G15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$G$6,'Boss Arena'!$G$7,'Boss Arena'!$G$8,'Boss Arena'!$G$9,'Boss Arena'!$G$10,'Boss Arena'!$G$11,'Boss Arena'!$G$12,'Boss Arena'!$G$13,'Boss Arena'!$G$14,'Boss Arena'!$G$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$G$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$G$6),ISERROR('Boss Arena'!$G$7),ISERROR('Boss Arena'!$G$8),ISERROR('Boss Arena'!$G$9),ISERROR('Boss Arena'!$G$10),ISERROR('Boss Arena'!$G$11),ISERROR('Boss Arena'!$G$12),ISERROR('Boss Arena'!$G$13),ISERROR('Boss Arena'!$G$14),ISERROR('Boss Arena'!$G$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$G$6),'Boss Arena'!$G$6=Key!$E$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$7),'Boss Arena'!$G$7=Key!$F$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$8),'Boss Arena'!$G$8=Key!$G$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$9),'Boss Arena'!$G$9=Key!$H$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$10),'Boss Arena'!$G$10=Key!$I$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$11),'Boss Arena'!$G$11=Key!$J$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$12),'Boss Arena'!$G$12=Key!$K$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$13),'Boss Arena'!$G$13=Key!$L$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$14),'Boss Arena'!$G$14=Key!$M$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$15),'Boss Arena'!$G$15=Key!$N$109),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$G$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use AND"))))),"LOCKED")</f>
@@ -5061,14 +5082,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B28" s="31" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In H6 return ""Star"" when Score is 95+ OR Age is 40+, otherwise ""No"". Fill down to H15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$H$6,'Boss Arena'!$H$7,'Boss Arena'!$H$8,'Boss Arena'!$H$9,'Boss Arena'!$H$10,'Boss Arena'!$H$11,'Boss Arena'!$H$12,'Boss Arena'!$H$13,'Boss Arena'!$H$14,'Boss Arena'!$H$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$H$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$H$6),ISERROR('Boss Arena'!$H$7),ISERROR('Boss Arena'!$H$8),ISERROR('Boss Arena'!$H$9),ISERROR('Boss Arena'!$H$10),ISERROR('Boss Arena'!$H$11),ISERROR('Boss Arena'!$H$12),ISERROR('Boss Arena'!$H$13),ISERROR('Boss Arena'!$H$14),ISERROR('Boss Arena'!$H$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$H$6),'Boss Arena'!$H$6=Key!$E$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$7),'Boss Arena'!$H$7=Key!$F$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$8),'Boss Arena'!$H$8=Key!$G$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$9),'Boss Arena'!$H$9=Key!$H$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$10),'Boss Arena'!$H$10=Key!$I$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$11),'Boss Arena'!$H$11=Key!$J$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$12),'Boss Arena'!$H$12=Key!$K$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$13),'Boss Arena'!$H$13=Key!$L$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$14),'Boss Arena'!$H$14=Key!$M$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$15),'Boss Arena'!$H$15=Key!$N$110),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"OR"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$H$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use OR"))))),"LOCKED")</f>
@@ -5086,14 +5107,14 @@
     </row>
     <row r="29" spans="1:7" ht="51.25" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B29" s="31" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In I6 use IFS: ""Gold"" for 90+, ""Silver"" for 75+, ""Bronze"" for 60+, otherwise ""None"". Fill down.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$I$6,'Boss Arena'!$I$7,'Boss Arena'!$I$8,'Boss Arena'!$I$9,'Boss Arena'!$I$10,'Boss Arena'!$I$11,'Boss Arena'!$I$12,'Boss Arena'!$I$13,'Boss Arena'!$I$14,'Boss Arena'!$I$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$I$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$I$6),ISERROR('Boss Arena'!$I$7),ISERROR('Boss Arena'!$I$8),ISERROR('Boss Arena'!$I$9),ISERROR('Boss Arena'!$I$10),ISERROR('Boss Arena'!$I$11),ISERROR('Boss Arena'!$I$12),ISERROR('Boss Arena'!$I$13),ISERROR('Boss Arena'!$I$14),ISERROR('Boss Arena'!$I$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$I$6),'Boss Arena'!$I$6=Key!$E$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$7),'Boss Arena'!$I$7=Key!$F$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$8),'Boss Arena'!$I$8=Key!$G$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$9),'Boss Arena'!$I$9=Key!$H$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$10),'Boss Arena'!$I$10=Key!$I$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$11),'Boss Arena'!$I$11=Key!$J$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$12),'Boss Arena'!$I$12=Key!$K$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$13),'Boss Arena'!$I$13=Key!$L$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$14),'Boss Arena'!$I$14=Key!$M$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$15),'Boss Arena'!$I$15=Key!$N$111),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$I$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFS"))))),"LOCKED")</f>
@@ -5111,14 +5132,14 @@
     </row>
     <row r="30" spans="1:7" ht="51.25" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B30" s="31" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In J6 return ""VIP"" for Score 80+ AND Age 18+, otherwise ""Member"" for Score 60+, otherwise ""Guest"". Fill down to J15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$J$6,'Boss Arena'!$J$7,'Boss Arena'!$J$8,'Boss Arena'!$J$9,'Boss Arena'!$J$10,'Boss Arena'!$J$11,'Boss Arena'!$J$12,'Boss Arena'!$J$13,'Boss Arena'!$J$14,'Boss Arena'!$J$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$J$6),ISERROR('Boss Arena'!$J$7),ISERROR('Boss Arena'!$J$8),ISERROR('Boss Arena'!$J$9),ISERROR('Boss Arena'!$J$10),ISERROR('Boss Arena'!$J$11),ISERROR('Boss Arena'!$J$12),ISERROR('Boss Arena'!$J$13),ISERROR('Boss Arena'!$J$14),ISERROR('Boss Arena'!$J$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$6),'Boss Arena'!$J$6=Key!$E$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$7),'Boss Arena'!$J$7=Key!$F$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$8),'Boss Arena'!$J$8=Key!$G$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$9),'Boss Arena'!$J$9=Key!$H$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$10),'Boss Arena'!$J$10=Key!$I$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$11),'Boss Arena'!$J$11=Key!$J$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$12),'Boss Arena'!$J$12=Key!$K$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$13),'Boss Arena'!$J$13=Key!$L$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$14),'Boss Arena'!$J$14=Key!$M$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$15),'Boss Arena'!$J$15=Key!$N$112),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF and AND"))))),"LOCKED")</f>
@@ -5136,14 +5157,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B31" s="31" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In L6 return TRUE when Ava (row 6) is NOT licensed (E6 is not ""Yes""). Use NOT.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$L$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$L$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$L$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$L$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('Boss Arena'!$L$6),'Boss Arena'!$L$6=(Key!$C$113="TRUE")),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"NOT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$L$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use NOT"))))),"LOCKED")</f>
@@ -5161,14 +5182,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="B32" s="31" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In E21 divide Total by Units with an IFERROR shield (0 on errors). Fill down to E26.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$E$21,'Boss Arena'!$E$22,'Boss Arena'!$E$23,'Boss Arena'!$E$24,'Boss Arena'!$E$25,'Boss Arena'!$E$26)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$E$21)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$22)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$23)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$24)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$25)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$26))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$E$21),ISERROR('Boss Arena'!$E$22),ISERROR('Boss Arena'!$E$23),ISERROR('Boss Arena'!$E$24),ISERROR('Boss Arena'!$E$25),ISERROR('Boss Arena'!$E$26)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$E$21),ABS('Boss Arena'!$E$21-Key!$E$114)&lt;=1E-9*MAX(1,ABS(Key!$E$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$22),ABS('Boss Arena'!$E$22-Key!$F$114)&lt;=1E-9*MAX(1,ABS(Key!$F$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$23),ABS('Boss Arena'!$E$23-Key!$G$114)&lt;=1E-9*MAX(1,ABS(Key!$G$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$24),ABS('Boss Arena'!$E$24-Key!$H$114)&lt;=1E-9*MAX(1,ABS(Key!$H$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$25),ABS('Boss Arena'!$E$25-Key!$I$114)&lt;=1E-9*MAX(1,ABS(Key!$I$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$26),ABS('Boss Arena'!$E$26-Key!$J$114)&lt;=1E-9*MAX(1,ABS(Key!$J$114))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFERROR"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$E$21)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFERROR"))))),"LOCKED")</f>
@@ -5186,14 +5207,14 @@
     </row>
     <row r="33" spans="1:7" ht="51.25" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="B33" s="31" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In H21 show ""Missing"" when the Name (G21) is empty, otherwise ""OK"" (use ISBLANK). Fill down to H25.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$H$21,'Boss Arena'!$H$22,'Boss Arena'!$H$23,'Boss Arena'!$H$24,'Boss Arena'!$H$25)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$H$21)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$22)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$23)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$24)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$25))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$H$21),ISERROR('Boss Arena'!$H$22),ISERROR('Boss Arena'!$H$23),ISERROR('Boss Arena'!$H$24),ISERROR('Boss Arena'!$H$25)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$H$21),'Boss Arena'!$H$21=Key!$E$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$22),'Boss Arena'!$H$22=Key!$F$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$23),'Boss Arena'!$H$23=Key!$G$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$24),'Boss Arena'!$H$24=Key!$H$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$25),'Boss Arena'!$H$25=Key!$I$115),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ISBLANK"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$H$21)))))),"✔ CLEAR","✘ CLOSE · right value, but use ISBLANK"))))),"LOCKED")</f>
@@ -5686,7 +5707,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5694,245 +5715,245 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>163</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>124</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.75" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>205</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>245</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.75" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>203</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>293</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>113</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>442</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>292</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.75" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>204</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>447</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -8085,33 +8106,33 @@
         <v>581</v>
       </c>
       <c r="B107" t="s">
-        <v>291</v>
+        <v>582</v>
       </c>
       <c r="E107" t="s">
-        <v>303</v>
+        <v>583</v>
       </c>
       <c r="F107" t="s">
-        <v>304</v>
+        <v>584</v>
       </c>
       <c r="G107" t="s">
-        <v>305</v>
+        <v>585</v>
       </c>
       <c r="H107" t="s">
-        <v>205</v>
+        <v>586</v>
       </c>
       <c r="I107" t="s">
-        <v>306</v>
+        <v>587</v>
       </c>
       <c r="J107" t="s">
-        <v>307</v>
+        <v>588</v>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B108" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="E108" cm="1" t="str">
         <f t="array" ref="E108">IF('Boss Arena'!$C$6&gt;=60,"Pass","Fail")</f>
@@ -8156,10 +8177,10 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B109" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="E109" cm="1" t="str">
         <f t="array" ref="E109">IF(AND('Boss Arena'!$D$6&gt;=18,'Boss Arena'!$C$6&gt;=70),"Yes","No")</f>
@@ -8204,10 +8225,10 @@
     </row>
     <row r="110" spans="1:14">
       <c r="A110" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B110" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="E110" cm="1" t="str">
         <f t="array" ref="E110">IF(OR('Boss Arena'!$C$6&gt;=95,'Boss Arena'!$D$6&gt;=40),"Star","No")</f>
@@ -8252,10 +8273,10 @@
     </row>
     <row r="111" spans="1:14">
       <c r="A111" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B111" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="E111" cm="1" t="str">
         <f t="array" ref="E111">_xlfn.IFS('Boss Arena'!$C$6&gt;=90,"Gold",'Boss Arena'!$C$6&gt;=75,"Silver",'Boss Arena'!$C$6&gt;=60,"Bronze",TRUE,"None")</f>
@@ -8300,10 +8321,10 @@
     </row>
     <row r="112" spans="1:14">
       <c r="A112" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="B112" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E112" cm="1" t="str">
         <f t="array" ref="E112">IF(AND('Boss Arena'!$C$6&gt;=80,'Boss Arena'!$D$6&gt;=18),"VIP",IF('Boss Arena'!$C$6&gt;=60,"Member","Guest"))</f>
@@ -8348,10 +8369,10 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="B113" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="C113" cm="1" t="str">
         <f t="array" ref="C113">IF(NOT('Boss Arena'!$E$6="Yes"),"TRUE","FALSE")</f>
@@ -8360,10 +8381,10 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="B114" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="E114" cm="1">
         <f t="array" ref="E114">IFERROR('Boss Arena'!$C$21/'Boss Arena'!$D$21,0)</f>
@@ -8392,10 +8413,10 @@
     </row>
     <row r="115" spans="1:10">
       <c r="A115" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="B115" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="E115" cm="1" t="str">
         <f t="array" ref="E115">IF(ISBLANK('Boss Arena'!$G$21),"Missing","OK")</f>

--- a/workbooks/04 Formulas 2 - Logic.xlsx
+++ b/workbooks/04 Formulas 2 - Logic.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="702">
   <si>
     <t>Challenge</t>
   </si>
@@ -535,43 +535,46 @@
     <t>T3</t>
   </si>
   <si>
+    <t>Which move is this? Text inside a formula goes in double quotes.</t>
+  </si>
+  <si>
+    <t>CHALLENGES · recall it, then do it</t>
+  </si>
+  <si>
+    <t>▶ Open F2-1 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F2-1 True or False C1</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>F2-1 True or False C2</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>F2-1 True or False C3</t>
+  </si>
+  <si>
+    <t>"</t>
+  </si>
+  <si>
+    <t>DOUBLEQUOTES</t>
+  </si>
+  <si>
+    <t>QUOTATIONMARKS</t>
+  </si>
+  <si>
+    <t>QUOTES</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
     <t>What must surround text inside a formula?</t>
-  </si>
-  <si>
-    <t>CHALLENGES · recall it, then do it</t>
-  </si>
-  <si>
-    <t>▶ Open F2-1 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F2-1 True or False C1</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>F2-1 True or False C2</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>F2-1 True or False C3</t>
-  </si>
-  <si>
-    <t>"</t>
-  </si>
-  <si>
-    <t>DOUBLEQUOTES</t>
-  </si>
-  <si>
-    <t>QUOTATIONMARKS</t>
-  </si>
-  <si>
-    <t>QUOTES</t>
-  </si>
-  <si>
-    <t>C3</t>
   </si>
   <si>
     <t>F2-1 True or False C4</t>
@@ -880,43 +883,46 @@
     <t>50 is not more than 100.</t>
   </si>
   <si>
+    <t>Which move is this? Each branch can be a calculation, not just text.</t>
+  </si>
+  <si>
+    <t>F2-2 Fork in the Road T3</t>
+  </si>
+  <si>
+    <t>Two double quotes, nothing inside.</t>
+  </si>
+  <si>
+    <t>What do you type in a formula for an empty, blank-looking result?</t>
+  </si>
+  <si>
+    <t>▶ Open F2-2 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F2-2 Fork in the Road C1</t>
+  </si>
+  <si>
+    <t>=IF</t>
+  </si>
+  <si>
+    <t>=IF(</t>
+  </si>
+  <si>
+    <t>=IF()</t>
+  </si>
+  <si>
+    <t>IF(</t>
+  </si>
+  <si>
+    <t>IF()</t>
+  </si>
+  <si>
+    <t>F2-2 Fork in the Road C2</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
     <t>In =IF(B2&gt;100,B2*0.9,B2), what is returned when B2 is 50?</t>
-  </si>
-  <si>
-    <t>F2-2 Fork in the Road T3</t>
-  </si>
-  <si>
-    <t>Two double quotes, nothing inside.</t>
-  </si>
-  <si>
-    <t>What do you type in a formula for an empty, blank-looking result?</t>
-  </si>
-  <si>
-    <t>▶ Open F2-2 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F2-2 Fork in the Road C1</t>
-  </si>
-  <si>
-    <t>=IF</t>
-  </si>
-  <si>
-    <t>=IF(</t>
-  </si>
-  <si>
-    <t>=IF()</t>
-  </si>
-  <si>
-    <t>IF(</t>
-  </si>
-  <si>
-    <t>IF()</t>
-  </si>
-  <si>
-    <t>F2-2 Fork in the Road C2</t>
-  </si>
-  <si>
-    <t>50</t>
   </si>
   <si>
     <t>F2-2 Fork in the Road C3</t>
@@ -1618,58 +1624,64 @@
     <t>One fewer than the outcomes.</t>
   </si>
   <si>
+    <t>Which move is this? Put an IF in the 'false' slot to handle three or more outcomes.</t>
+  </si>
+  <si>
+    <t>F2-4 Multi-Level T2</t>
+  </si>
+  <si>
+    <t>IF plus one letter.</t>
+  </si>
+  <si>
+    <t>Which function tests several conditions in order without nesting?</t>
+  </si>
+  <si>
+    <t>F2-4 Multi-Level T3</t>
+  </si>
+  <si>
+    <t>A test that is always true.</t>
+  </si>
+  <si>
+    <t>Which move is this? End IFS with TRUE and a fallback to catch everything else.</t>
+  </si>
+  <si>
+    <t>▶ Open F2-4 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F2-4 Multi-Level C1</t>
+  </si>
+  <si>
+    <t>TWO</t>
+  </si>
+  <si>
     <t>How many IF functions does a nested IF need for 3 outcomes?</t>
   </si>
   <si>
-    <t>F2-4 Multi-Level T2</t>
-  </si>
-  <si>
-    <t>IF plus one letter.</t>
-  </si>
-  <si>
-    <t>Which function tests several conditions in order without nesting?</t>
-  </si>
-  <si>
-    <t>F2-4 Multi-Level T3</t>
-  </si>
-  <si>
-    <t>A test that is always true.</t>
+    <t>F2-4 Multi-Level C2</t>
+  </si>
+  <si>
+    <t>=IFS</t>
+  </si>
+  <si>
+    <t>=IFS(</t>
+  </si>
+  <si>
+    <t>=IFS()</t>
+  </si>
+  <si>
+    <t>IFS(</t>
+  </si>
+  <si>
+    <t>IFS()</t>
+  </si>
+  <si>
+    <t>F2-4 Multi-Level C3</t>
+  </si>
+  <si>
+    <t>TRUE</t>
   </si>
   <si>
     <t>In IFS, what do you put as the last test to catch all remaining cases?</t>
-  </si>
-  <si>
-    <t>▶ Open F2-4 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F2-4 Multi-Level C1</t>
-  </si>
-  <si>
-    <t>TWO</t>
-  </si>
-  <si>
-    <t>F2-4 Multi-Level C2</t>
-  </si>
-  <si>
-    <t>=IFS</t>
-  </si>
-  <si>
-    <t>=IFS(</t>
-  </si>
-  <si>
-    <t>=IFS()</t>
-  </si>
-  <si>
-    <t>IFS(</t>
-  </si>
-  <si>
-    <t>IFS()</t>
-  </si>
-  <si>
-    <t>F2-4 Multi-Level C3</t>
-  </si>
-  <si>
-    <t>TRUE</t>
   </si>
   <si>
     <t>F2-4 Multi-Level C4</t>
@@ -3350,7 +3362,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3360,12 +3372,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3375,32 +3387,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3410,7 +3422,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
@@ -3419,21 +3431,21 @@
         <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F2-1 True or False'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3448,15 +3460,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F2-2 Fork in the Road'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3471,15 +3483,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F2-3 Combo Moves'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3494,15 +3506,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F2-4 Multi-Level'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3517,15 +3529,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM('F2-5 Error Shield'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3540,15 +3552,15 @@
         <v>NEW</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C18" s="9" cm="1" t="str">
         <f t="array" ref="C18">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3563,12 +3575,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">(SUM('F2-1 True or False'!$G$13:$G$38)+SUM('F2-2 Fork in the Road'!$G$13:$G$38)+SUM('F2-3 Combo Moves'!$G$13:$G$38)+SUM('F2-4 Multi-Level'!$G$13:$G$38)+SUM('F2-5 Error Shield'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 1140"</f>
@@ -3577,19 +3589,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">_xlfn.LET(_xlpm.p,(SUM('F2-1 True or False'!$G$13:$G$38)+SUM('F2-2 Fork in the Road'!$G$13:$G$38)+SUM('F2-3 Combo Moves'!$G$13:$G$38)+SUM('F2-4 Multi-Level'!$G$13:$G$38)+SUM('F2-5 Error Shield'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))/1140,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3598,7 +3610,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="7" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B23" s="12" cm="1" t="str">
         <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3607,7 +3619,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="13" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -3645,7 +3657,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3656,7 +3668,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3708,10 +3720,10 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="51.25" customHeight="1">
@@ -3719,10 +3731,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.5" customHeight="1">
@@ -3730,21 +3742,21 @@
         <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="51.25" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
@@ -3786,7 +3798,7 @@
         <v>50</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -3808,7 +3820,7 @@
         <v>55</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -3830,7 +3842,7 @@
         <v>60</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -3852,7 +3864,7 @@
         <v>65</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -3874,7 +3886,7 @@
         <v>70</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -3896,7 +3908,7 @@
         <v>75</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -3918,7 +3930,7 @@
         <v>80</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -3940,7 +3952,7 @@
         <v>85</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -3962,7 +3974,7 @@
         <v>94</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -3984,7 +3996,7 @@
         <v>108</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -4040,7 +4052,7 @@
         <v>114</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -4062,7 +4074,7 @@
         <v>120</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -4084,7 +4096,7 @@
         <v>125</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -4103,10 +4115,10 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -4136,7 +4148,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="11" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -4167,7 +4179,7 @@
         <v>130</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -4189,7 +4201,7 @@
         <v>132</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -4211,7 +4223,7 @@
         <v>138</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -4230,10 +4242,10 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -4252,13 +4264,13 @@
     </row>
     <row r="39" spans="1:7" ht="51.25" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(COUNTA('F2-5 Arena'!$E$6,'F2-5 Arena'!$E$7,'F2-5 Arena'!$E$8,'F2-5 Arena'!$E$9,'F2-5 Arena'!$E$10,'F2-5 Arena'!$E$11)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$6)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$7)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$8)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$9)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$10)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$11))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-5 Arena'!$E$6),ISERROR('F2-5 Arena'!$E$7),ISERROR('F2-5 Arena'!$E$8),ISERROR('F2-5 Arena'!$E$9),ISERROR('F2-5 Arena'!$E$10),ISERROR('F2-5 Arena'!$E$11)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$6),ABS('F2-5 Arena'!$E$6-Key!$E$96)&lt;=1E-9*MAX(1,ABS(Key!$E$96))),FALSE),IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$7),ABS('F2-5 Arena'!$E$7-Key!$F$96)&lt;=1E-9*MAX(1,ABS(Key!$F$96))),FALSE),IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$8),ABS('F2-5 Arena'!$E$8-Key!$G$96)&lt;=1E-9*MAX(1,ABS(Key!$G$96))),FALSE),IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$9),ABS('F2-5 Arena'!$E$9-Key!$H$96)&lt;=1E-9*MAX(1,ABS(Key!$H$96))),FALSE),IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$10),ABS('F2-5 Arena'!$E$10-Key!$I$96)&lt;=1E-9*MAX(1,ABS(Key!$I$96))),FALSE),IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$11),ABS('F2-5 Arena'!$E$11-Key!$J$96)&lt;=1E-9*MAX(1,ABS(Key!$J$96))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFERROR"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-5 Arena'!$E$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFERROR")))))</f>
@@ -4276,13 +4288,13 @@
     </row>
     <row r="40" spans="1:7" ht="35.5" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D40" s="21" cm="1" t="str">
         <f t="array" ref="D40">IF(ISBLANK('F2-5 Arena'!$F$14),"",IF(NOT(_xlfn.ISFORMULA('F2-5 Arena'!$F$14)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-5 Arena'!$F$14),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-5 Arena'!$F$14),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F2-5 Arena'!$F$14),'F2-5 Arena'!$F$14=Key!$C$97),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFNA"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-5 Arena'!$F$14)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFNA")))))</f>
@@ -4300,13 +4312,13 @@
     </row>
     <row r="41" spans="1:7" ht="51.25" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D41" s="21" cm="1" t="str">
         <f t="array" ref="D41">IF(COUNTA('F2-5 Arena'!$C$17,'F2-5 Arena'!$C$18,'F2-5 Arena'!$C$19,'F2-5 Arena'!$C$20,'F2-5 Arena'!$C$21)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-5 Arena'!$C$17)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$C$18)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$C$19)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$C$20)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$C$21))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-5 Arena'!$C$17),ISERROR('F2-5 Arena'!$C$18),ISERROR('F2-5 Arena'!$C$19),ISERROR('F2-5 Arena'!$C$20),ISERROR('F2-5 Arena'!$C$21)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-5 Arena'!$C$17),'F2-5 Arena'!$C$17=Key!$E$98),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$C$18),'F2-5 Arena'!$C$18=Key!$F$98),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$C$19),'F2-5 Arena'!$C$19=Key!$G$98),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$C$20),'F2-5 Arena'!$C$20=Key!$H$98),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$C$21),'F2-5 Arena'!$C$21=Key!$I$98),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ISBLANK"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-5 Arena'!$C$17)))))),"✔ CLEAR","✘ CLOSE · right value, but use ISBLANK")))))</f>
@@ -4324,13 +4336,13 @@
     </row>
     <row r="42" spans="1:7" ht="51.25" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(COUNTA('F2-5 Arena'!$E$23,'F2-5 Arena'!$E$24,'F2-5 Arena'!$E$25,'F2-5 Arena'!$E$26,'F2-5 Arena'!$E$27)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$23)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$24)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$25)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$26)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$27))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-5 Arena'!$E$23),ISERROR('F2-5 Arena'!$E$24),ISERROR('F2-5 Arena'!$E$25),ISERROR('F2-5 Arena'!$E$26),ISERROR('F2-5 Arena'!$E$27)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-5 Arena'!$E$23),'F2-5 Arena'!$E$23=Key!$E$99),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$E$24),'F2-5 Arena'!$E$24=Key!$F$99),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$E$25),'F2-5 Arena'!$E$25=Key!$G$99),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$E$26),'F2-5 Arena'!$E$26=Key!$H$99),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$E$27),'F2-5 Arena'!$E$27=Key!$I$99),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ISNUMBER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-5 Arena'!$E$23)))))),"✔ CLEAR","✘ CLOSE · right value, but use ISNUMBER")))))</f>
@@ -4476,7 +4488,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4489,29 +4501,29 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="27" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="5" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C6" s="5">
         <v>120</v>
@@ -4523,7 +4535,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="5" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C7" s="5">
         <v>90</v>
@@ -4535,7 +4547,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="5" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C8" s="5">
         <v>60</v>
@@ -4547,7 +4559,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
@@ -4559,7 +4571,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="5" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C10" s="5">
         <v>45</v>
@@ -4571,7 +4583,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="B11" s="5" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C11" s="5">
         <v>30</v>
@@ -4583,14 +4595,14 @@
     </row>
     <row r="14" spans="1:6">
       <c r="B14" s="7" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D14" s="5" cm="1" t="str">
         <f t="array" ref="D14">NA()</f>
         <v>#N/A</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F14" s="28"/>
     </row>
@@ -4599,7 +4611,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -4628,10 +4640,10 @@
     </row>
     <row r="22" spans="2:5">
       <c r="D22" s="27" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -4642,7 +4654,7 @@
     </row>
     <row r="24" spans="2:5">
       <c r="D24" s="5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E24" s="28"/>
     </row>
@@ -4654,7 +4666,7 @@
     </row>
     <row r="26" spans="2:5">
       <c r="D26" s="5" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E26" s="28"/>
     </row>
@@ -4692,7 +4704,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4703,7 +4715,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -4722,7 +4734,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4733,19 +4745,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C6" s="29"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C8" s="30" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -4754,7 +4766,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C9" s="30">
         <v>15</v>
@@ -4762,7 +4774,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F2-1 True or False'!$G$13:$G$38)&gt;=190*0.5,SUM('F2-2 Fork in the Road'!$G$13:$G$38)&gt;=190*0.5,SUM('F2-3 Combo Moves'!$G$13:$G$38)&gt;=190*0.5,SUM('F2-4 Multi-Level'!$G$13:$G$38)&gt;=190*0.5,SUM('F2-5 Error Shield'!$G$14:$G$42)&gt;=220*0.5),"OPEN","LOCKED")</f>
@@ -4775,7 +4787,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4809,7 +4821,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B14" s="31" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which function replaces any error with your own value?  (from F2-5 Error Shield)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4832,7 +4844,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B15" s="31" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","Which function replaces only the #N/A error?  (from F2-5 Error Shield)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4855,7 +4867,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B16" s="31" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which function is TRUE when a cell is empty?  (from F2-5 Error Shield)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4878,7 +4890,7 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B17" s="31" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","Which function is TRUE when a value is a number?  (from F2-5 Error Shield)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4901,7 +4913,7 @@
     </row>
     <row r="18" spans="1:7" ht="51.25" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B18" s="31" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which function returns one value when a test is TRUE and another when FALSE?  (from F2-2 Fork in the Road)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4924,7 +4936,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B19" s="31" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","In =IF"&amp;"(B2&gt;100,B2*0.9,B2), what is returned when B2 is 50?  (from F2-2 Fork in the Road)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4947,7 +4959,7 @@
     </row>
     <row r="20" spans="1:7" ht="51.25" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B20" s="31" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","What do you type in a formula for an empty, blank-looking result?  (from F2-2 Fork in the Road)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4970,7 +4982,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B21" s="31" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which function counts every non-empty cell?  (from F1-2 Big Six)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4993,7 +5005,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -5004,7 +5016,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5032,14 +5044,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B26" s="31" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In F6 return ""Pass"" for a Score of 60 or more, otherwise ""Fail"". Fill down to F15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$F$6,'Boss Arena'!$F$7,'Boss Arena'!$F$8,'Boss Arena'!$F$9,'Boss Arena'!$F$10,'Boss Arena'!$F$11,'Boss Arena'!$F$12,'Boss Arena'!$F$13,'Boss Arena'!$F$14,'Boss Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$F$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$F$6),ISERROR('Boss Arena'!$F$7),ISERROR('Boss Arena'!$F$8),ISERROR('Boss Arena'!$F$9),ISERROR('Boss Arena'!$F$10),ISERROR('Boss Arena'!$F$11),ISERROR('Boss Arena'!$F$12),ISERROR('Boss Arena'!$F$13),ISERROR('Boss Arena'!$F$14),ISERROR('Boss Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$F$6),'Boss Arena'!$F$6=Key!$E$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$7),'Boss Arena'!$F$7=Key!$F$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$8),'Boss Arena'!$F$8=Key!$G$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$9),'Boss Arena'!$F$9=Key!$H$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$10),'Boss Arena'!$F$10=Key!$I$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$11),'Boss Arena'!$F$11=Key!$J$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$12),'Boss Arena'!$F$12=Key!$K$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$13),'Boss Arena'!$F$13=Key!$L$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$14),'Boss Arena'!$F$14=Key!$M$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$15),'Boss Arena'!$F$15=Key!$N$108),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$F$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF"))))),"LOCKED")</f>
@@ -5057,14 +5069,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B27" s="31" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In G6 return ""Yes"" when Age is 18+ AND Score is 70+, otherwise ""No"". Fill down to G15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$G$6,'Boss Arena'!$G$7,'Boss Arena'!$G$8,'Boss Arena'!$G$9,'Boss Arena'!$G$10,'Boss Arena'!$G$11,'Boss Arena'!$G$12,'Boss Arena'!$G$13,'Boss Arena'!$G$14,'Boss Arena'!$G$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$G$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$G$6),ISERROR('Boss Arena'!$G$7),ISERROR('Boss Arena'!$G$8),ISERROR('Boss Arena'!$G$9),ISERROR('Boss Arena'!$G$10),ISERROR('Boss Arena'!$G$11),ISERROR('Boss Arena'!$G$12),ISERROR('Boss Arena'!$G$13),ISERROR('Boss Arena'!$G$14),ISERROR('Boss Arena'!$G$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$G$6),'Boss Arena'!$G$6=Key!$E$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$7),'Boss Arena'!$G$7=Key!$F$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$8),'Boss Arena'!$G$8=Key!$G$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$9),'Boss Arena'!$G$9=Key!$H$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$10),'Boss Arena'!$G$10=Key!$I$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$11),'Boss Arena'!$G$11=Key!$J$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$12),'Boss Arena'!$G$12=Key!$K$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$13),'Boss Arena'!$G$13=Key!$L$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$14),'Boss Arena'!$G$14=Key!$M$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$15),'Boss Arena'!$G$15=Key!$N$109),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$G$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use AND"))))),"LOCKED")</f>
@@ -5082,14 +5094,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B28" s="31" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In H6 return ""Star"" when Score is 95+ OR Age is 40+, otherwise ""No"". Fill down to H15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$H$6,'Boss Arena'!$H$7,'Boss Arena'!$H$8,'Boss Arena'!$H$9,'Boss Arena'!$H$10,'Boss Arena'!$H$11,'Boss Arena'!$H$12,'Boss Arena'!$H$13,'Boss Arena'!$H$14,'Boss Arena'!$H$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$H$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$H$6),ISERROR('Boss Arena'!$H$7),ISERROR('Boss Arena'!$H$8),ISERROR('Boss Arena'!$H$9),ISERROR('Boss Arena'!$H$10),ISERROR('Boss Arena'!$H$11),ISERROR('Boss Arena'!$H$12),ISERROR('Boss Arena'!$H$13),ISERROR('Boss Arena'!$H$14),ISERROR('Boss Arena'!$H$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$H$6),'Boss Arena'!$H$6=Key!$E$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$7),'Boss Arena'!$H$7=Key!$F$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$8),'Boss Arena'!$H$8=Key!$G$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$9),'Boss Arena'!$H$9=Key!$H$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$10),'Boss Arena'!$H$10=Key!$I$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$11),'Boss Arena'!$H$11=Key!$J$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$12),'Boss Arena'!$H$12=Key!$K$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$13),'Boss Arena'!$H$13=Key!$L$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$14),'Boss Arena'!$H$14=Key!$M$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$15),'Boss Arena'!$H$15=Key!$N$110),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"OR"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$H$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use OR"))))),"LOCKED")</f>
@@ -5107,14 +5119,14 @@
     </row>
     <row r="29" spans="1:7" ht="51.25" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B29" s="31" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In I6 use IFS: ""Gold"" for 90+, ""Silver"" for 75+, ""Bronze"" for 60+, otherwise ""None"". Fill down.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$I$6,'Boss Arena'!$I$7,'Boss Arena'!$I$8,'Boss Arena'!$I$9,'Boss Arena'!$I$10,'Boss Arena'!$I$11,'Boss Arena'!$I$12,'Boss Arena'!$I$13,'Boss Arena'!$I$14,'Boss Arena'!$I$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$I$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$I$6),ISERROR('Boss Arena'!$I$7),ISERROR('Boss Arena'!$I$8),ISERROR('Boss Arena'!$I$9),ISERROR('Boss Arena'!$I$10),ISERROR('Boss Arena'!$I$11),ISERROR('Boss Arena'!$I$12),ISERROR('Boss Arena'!$I$13),ISERROR('Boss Arena'!$I$14),ISERROR('Boss Arena'!$I$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$I$6),'Boss Arena'!$I$6=Key!$E$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$7),'Boss Arena'!$I$7=Key!$F$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$8),'Boss Arena'!$I$8=Key!$G$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$9),'Boss Arena'!$I$9=Key!$H$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$10),'Boss Arena'!$I$10=Key!$I$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$11),'Boss Arena'!$I$11=Key!$J$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$12),'Boss Arena'!$I$12=Key!$K$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$13),'Boss Arena'!$I$13=Key!$L$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$14),'Boss Arena'!$I$14=Key!$M$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$15),'Boss Arena'!$I$15=Key!$N$111),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$I$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFS"))))),"LOCKED")</f>
@@ -5132,14 +5144,14 @@
     </row>
     <row r="30" spans="1:7" ht="51.25" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B30" s="31" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In J6 return ""VIP"" for Score 80+ AND Age 18+, otherwise ""Member"" for Score 60+, otherwise ""Guest"". Fill down to J15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$J$6,'Boss Arena'!$J$7,'Boss Arena'!$J$8,'Boss Arena'!$J$9,'Boss Arena'!$J$10,'Boss Arena'!$J$11,'Boss Arena'!$J$12,'Boss Arena'!$J$13,'Boss Arena'!$J$14,'Boss Arena'!$J$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$J$6),ISERROR('Boss Arena'!$J$7),ISERROR('Boss Arena'!$J$8),ISERROR('Boss Arena'!$J$9),ISERROR('Boss Arena'!$J$10),ISERROR('Boss Arena'!$J$11),ISERROR('Boss Arena'!$J$12),ISERROR('Boss Arena'!$J$13),ISERROR('Boss Arena'!$J$14),ISERROR('Boss Arena'!$J$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$6),'Boss Arena'!$J$6=Key!$E$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$7),'Boss Arena'!$J$7=Key!$F$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$8),'Boss Arena'!$J$8=Key!$G$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$9),'Boss Arena'!$J$9=Key!$H$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$10),'Boss Arena'!$J$10=Key!$I$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$11),'Boss Arena'!$J$11=Key!$J$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$12),'Boss Arena'!$J$12=Key!$K$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$13),'Boss Arena'!$J$13=Key!$L$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$14),'Boss Arena'!$J$14=Key!$M$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$15),'Boss Arena'!$J$15=Key!$N$112),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF and AND"))))),"LOCKED")</f>
@@ -5157,14 +5169,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B31" s="31" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In L6 return TRUE when Ava (row 6) is NOT licensed (E6 is not ""Yes""). Use NOT.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$L$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$L$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$L$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$L$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('Boss Arena'!$L$6),'Boss Arena'!$L$6=(Key!$C$113="TRUE")),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"NOT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$L$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use NOT"))))),"LOCKED")</f>
@@ -5182,14 +5194,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B32" s="31" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In E21 divide Total by Units with an IFERROR shield (0 on errors). Fill down to E26.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$E$21,'Boss Arena'!$E$22,'Boss Arena'!$E$23,'Boss Arena'!$E$24,'Boss Arena'!$E$25,'Boss Arena'!$E$26)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$E$21)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$22)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$23)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$24)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$25)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$26))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$E$21),ISERROR('Boss Arena'!$E$22),ISERROR('Boss Arena'!$E$23),ISERROR('Boss Arena'!$E$24),ISERROR('Boss Arena'!$E$25),ISERROR('Boss Arena'!$E$26)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$E$21),ABS('Boss Arena'!$E$21-Key!$E$114)&lt;=1E-9*MAX(1,ABS(Key!$E$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$22),ABS('Boss Arena'!$E$22-Key!$F$114)&lt;=1E-9*MAX(1,ABS(Key!$F$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$23),ABS('Boss Arena'!$E$23-Key!$G$114)&lt;=1E-9*MAX(1,ABS(Key!$G$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$24),ABS('Boss Arena'!$E$24-Key!$H$114)&lt;=1E-9*MAX(1,ABS(Key!$H$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$25),ABS('Boss Arena'!$E$25-Key!$I$114)&lt;=1E-9*MAX(1,ABS(Key!$I$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$26),ABS('Boss Arena'!$E$26-Key!$J$114)&lt;=1E-9*MAX(1,ABS(Key!$J$114))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFERROR"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$E$21)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFERROR"))))),"LOCKED")</f>
@@ -5207,14 +5219,14 @@
     </row>
     <row r="33" spans="1:7" ht="51.25" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B33" s="31" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In H21 show ""Missing"" when the Name (G21) is empty, otherwise ""OK"" (use ISBLANK). Fill down to H25.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$H$21,'Boss Arena'!$H$22,'Boss Arena'!$H$23,'Boss Arena'!$H$24,'Boss Arena'!$H$25)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$H$21)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$22)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$23)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$24)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$25))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$H$21),ISERROR('Boss Arena'!$H$22),ISERROR('Boss Arena'!$H$23),ISERROR('Boss Arena'!$H$24),ISERROR('Boss Arena'!$H$25)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$H$21),'Boss Arena'!$H$21=Key!$E$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$22),'Boss Arena'!$H$22=Key!$F$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$23),'Boss Arena'!$H$23=Key!$G$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$24),'Boss Arena'!$H$24=Key!$H$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$25),'Boss Arena'!$H$25=Key!$I$115),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ISBLANK"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$H$21)))))),"✔ CLEAR","✘ CLOSE · right value, but use ISBLANK"))))),"LOCKED")</f>
@@ -5334,7 +5346,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -5347,10 +5359,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -5367,22 +5379,22 @@
         <v>12</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -5578,27 +5590,27 @@
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="27" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="G20" s="27" t="s">
         <v>9</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="5" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C21" s="5">
         <v>120</v>
@@ -5614,7 +5626,7 @@
     </row>
     <row r="22" spans="2:8">
       <c r="B22" s="5" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C22" s="5">
         <v>90</v>
@@ -5627,7 +5639,7 @@
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="5" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C23" s="5">
         <v>60</v>
@@ -5643,7 +5655,7 @@
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C24" s="5">
         <v>0</v>
@@ -5656,7 +5668,7 @@
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="5" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C25" s="5">
         <v>45</v>
@@ -5672,7 +5684,7 @@
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="5" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C26" s="5">
         <v>30</v>
@@ -5707,7 +5719,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5715,245 +5727,245 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>124</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.75" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.75" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>113</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.75" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>
@@ -6244,10 +6256,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C18" cm="1" t="str">
         <f t="array" ref="C18">IF('F2-1 Arena'!$C$6&gt;=50,"TRUE","FALSE")</f>
@@ -6256,10 +6268,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C19" cm="1" t="str">
         <f t="array" ref="C19">IF('F2-1 Arena'!$E$7&lt;&gt;"No","TRUE","FALSE")</f>
@@ -6268,10 +6280,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C20" cm="1" t="str">
         <f t="array" ref="C20">IF('F2-1 Arena'!$E$8="yes","TRUE","FALSE")</f>
@@ -6280,7 +6292,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s">
         <v>112</v>
@@ -6291,7 +6303,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B22" t="s">
         <v>117</v>
@@ -6302,7 +6314,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B23" t="s">
         <v>123</v>
@@ -6322,113 +6334,113 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B25" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B30" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E30" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G31" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H31" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C32" t="s">
         <v>118</v>
@@ -6448,10 +6460,10 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C33" t="s">
         <v>124</v>
@@ -6471,47 +6483,47 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B34" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E34" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F34" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G34" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I34" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J34" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B35" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E35" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E36" t="s">
         <v>124</v>
@@ -6519,10 +6531,10 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B37" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E37" cm="1" t="str">
         <f t="array" ref="E37">IF('F2-2 Arena'!$C$6&gt;=50,"Pass","Fail")</f>
@@ -6567,10 +6579,10 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B38" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E38" cm="1">
         <f t="array" ref="E38">IF('F2-2 Arena'!$C$6&gt;=80,'F2-2 Arena'!$C$6*10,0)</f>
@@ -6615,10 +6627,10 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B39" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C39" cm="1" t="str">
         <f t="array" ref="C39">IF('F2-2 Arena'!$J$6="","",'F2-2 Arena'!$J$6*2)</f>
@@ -6627,47 +6639,47 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E41" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E42" t="s">
         <v>124</v>
@@ -6675,261 +6687,261 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E43" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F43" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E44" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F44" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G44" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H44" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I44" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J44" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K44" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B45" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E45" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B46" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E46" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B47" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E47" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F47" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B48" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E48" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F48" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B49" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E49" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B50" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C50" t="s">
+        <v>206</v>
+      </c>
+      <c r="E50" t="s">
+        <v>206</v>
+      </c>
+      <c r="F50" t="s">
+        <v>294</v>
+      </c>
+      <c r="G50" t="s">
         <v>205</v>
       </c>
-      <c r="E50" t="s">
-        <v>205</v>
-      </c>
-      <c r="F50" t="s">
-        <v>292</v>
-      </c>
-      <c r="G50" t="s">
-        <v>204</v>
-      </c>
       <c r="H50" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B51" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F51" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G51" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H51" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B52" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E52" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F52" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H52" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B53" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E53" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F53" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G53" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H53" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I53" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J53" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B54" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E54" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F54" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G54" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H54" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I54" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J54" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B55" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E55" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F55" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J55" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B56" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E56" cm="1" t="str">
         <f t="array" ref="E56">IF(AND('F2-3 Arena'!$D$6&gt;=18,'F2-3 Arena'!$E$6="Yes"),"Yes","No")</f>
@@ -6974,10 +6986,10 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B57" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E57" cm="1" t="str">
         <f t="array" ref="E57">IF(OR('F2-3 Arena'!$C$6&gt;=90,'F2-3 Arena'!$D$6&lt;16),"Prize","No prize")</f>
@@ -7022,10 +7034,10 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B58" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C58" cm="1" t="str">
         <f t="array" ref="C58">IF(NOT('F2-3 Arena'!$E$6="Yes"),"TRUE","FALSE")</f>
@@ -7034,207 +7046,207 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E59" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F59" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G59" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I59" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J59" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B60" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E60" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F60" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G60" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H60" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I60" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J60" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B61" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E61" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F61" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G61" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I61" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J61" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B62" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E62" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E63" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F63" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G63" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B64" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E64" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F64" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G64" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H64" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B65" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E65" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F65" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B66" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E66" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B67" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E67" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F67" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G67" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H67" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B68" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E68" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F68" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G68" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H68" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I68" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J68" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C69" t="s">
         <v>119</v>
@@ -7254,33 +7266,33 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B70" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C70" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E70" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F70" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G70" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H70" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B71" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C71" t="s">
         <v>113</v>
@@ -7300,61 +7312,61 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B72" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E72" t="s">
         <v>35</v>
       </c>
       <c r="F72" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B73" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E73" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F73" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="G73" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H73" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I73" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J73" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B74" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E74" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B75" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E75" cm="1" t="str">
         <f t="array" ref="E75">IF('F2-4 Arena'!$C$6&gt;=90,"A",IF('F2-4 Arena'!$C$6&gt;=75,"B","C"))</f>
@@ -7399,10 +7411,10 @@
     </row>
     <row r="76" spans="1:14">
       <c r="A76" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B76" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E76" cm="1" t="str">
         <f t="array" ref="E76">_xlfn.IFS('F2-4 Arena'!$C$6&gt;=90,"Gold",'F2-4 Arena'!$C$6&gt;=75,"Silver",'F2-4 Arena'!$C$6&gt;=60,"Bronze",TRUE,"None")</f>
@@ -7447,69 +7459,69 @@
     </row>
     <row r="77" spans="1:14">
       <c r="A77" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B77" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C77" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B78" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E78" t="s">
         <v>35</v>
       </c>
       <c r="F78" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B79" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E79" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F79" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="G79" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H79" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I79" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J79" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B80" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E80" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B81" t="s">
         <v>112</v>
@@ -7520,7 +7532,7 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B82" t="s">
         <v>117</v>
@@ -7531,7 +7543,7 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B83" t="s">
         <v>123</v>
@@ -7551,310 +7563,310 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B84" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E84" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F84" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="G84" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="H84" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="I84" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="J84" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B85" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E85" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F85" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G85" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H85" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="I85" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="J85" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B86" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E86" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F86" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="G86" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="H86" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="I86" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="J86" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E87" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F87" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="G87" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="H87" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="I87" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J87" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B88" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C88" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E88" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F88" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G88" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H88" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B89" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C89" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E89" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F89" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G89" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H89" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B90" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C90" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E90" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F90" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G90" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H90" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B91" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C91" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E91" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F91" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G91" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H91" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B92" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E92" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F92" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="G92" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="H92" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="I92" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J92" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B93" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E93" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F93" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="G93" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H93" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I93" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="J93" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B94" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E94" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F94" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G94" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="H94" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I94" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="J94" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B95" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E95" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F95" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G95" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="H95" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="I95" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="J95" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B96" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E96" cm="1">
         <f t="array" ref="E96">IFERROR('F2-5 Arena'!$C$6/'F2-5 Arena'!$D$6,0)</f>
@@ -7883,10 +7895,10 @@
     </row>
     <row r="97" spans="1:14">
       <c r="A97" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B97" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C97" cm="1" t="str">
         <f t="array" ref="C97">_xlfn.IFNA('F2-5 Arena'!$D$14,"Missing")</f>
@@ -7895,10 +7907,10 @@
     </row>
     <row r="98" spans="1:14">
       <c r="A98" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B98" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E98" cm="1" t="str">
         <f t="array" ref="E98">IF(ISBLANK('F2-5 Arena'!$B$17),"Missing","OK")</f>
@@ -7923,10 +7935,10 @@
     </row>
     <row r="99" spans="1:14">
       <c r="A99" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B99" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E99" cm="1" t="str">
         <f t="array" ref="E99">IF(ISNUMBER('F2-5 Arena'!$D$23),"Number","Text")</f>
@@ -7951,151 +7963,151 @@
     </row>
     <row r="100" spans="1:14">
       <c r="A100" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B100" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E100" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F100" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="G100" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="H100" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="I100" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J100" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B101" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E101" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F101" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="G101" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H101" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I101" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="J101" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B102" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E102" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F102" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G102" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="H102" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I102" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="J102" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B103" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E103" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F103" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G103" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="H103" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="I103" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="J103" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B104" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E104" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F104" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G104" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H104" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I104" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J104" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B105" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E105" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B106" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E106" t="s">
         <v>124</v>
@@ -8103,36 +8115,36 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B107" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="E107" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="F107" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="G107" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H107" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="I107" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="J107" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B108" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E108" cm="1" t="str">
         <f t="array" ref="E108">IF('Boss Arena'!$C$6&gt;=60,"Pass","Fail")</f>
@@ -8177,10 +8189,10 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B109" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E109" cm="1" t="str">
         <f t="array" ref="E109">IF(AND('Boss Arena'!$D$6&gt;=18,'Boss Arena'!$C$6&gt;=70),"Yes","No")</f>
@@ -8225,10 +8237,10 @@
     </row>
     <row r="110" spans="1:14">
       <c r="A110" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B110" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E110" cm="1" t="str">
         <f t="array" ref="E110">IF(OR('Boss Arena'!$C$6&gt;=95,'Boss Arena'!$D$6&gt;=40),"Star","No")</f>
@@ -8273,10 +8285,10 @@
     </row>
     <row r="111" spans="1:14">
       <c r="A111" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B111" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E111" cm="1" t="str">
         <f t="array" ref="E111">_xlfn.IFS('Boss Arena'!$C$6&gt;=90,"Gold",'Boss Arena'!$C$6&gt;=75,"Silver",'Boss Arena'!$C$6&gt;=60,"Bronze",TRUE,"None")</f>
@@ -8321,10 +8333,10 @@
     </row>
     <row r="112" spans="1:14">
       <c r="A112" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B112" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="E112" cm="1" t="str">
         <f t="array" ref="E112">IF(AND('Boss Arena'!$C$6&gt;=80,'Boss Arena'!$D$6&gt;=18),"VIP",IF('Boss Arena'!$C$6&gt;=60,"Member","Guest"))</f>
@@ -8369,10 +8381,10 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B113" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C113" cm="1" t="str">
         <f t="array" ref="C113">IF(NOT('Boss Arena'!$E$6="Yes"),"TRUE","FALSE")</f>
@@ -8381,10 +8393,10 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="E114" cm="1">
         <f t="array" ref="E114">IFERROR('Boss Arena'!$C$21/'Boss Arena'!$D$21,0)</f>
@@ -8413,10 +8425,10 @@
     </row>
     <row r="115" spans="1:10">
       <c r="A115" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B115" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="E115" cm="1" t="str">
         <f t="array" ref="E115">IF(ISBLANK('Boss Arena'!$G$21),"Missing","OK")</f>
@@ -8464,7 +8476,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8475,7 +8487,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8887,7 +8899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="19.75" customHeight="1">
+    <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
         <v>125</v>
       </c>
@@ -8997,7 +9009,7 @@
         <v>138</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -9016,13 +9028,13 @@
     </row>
     <row r="36" spans="1:7" ht="51.25" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F2-1 Arena'!$G$6),"",IF(NOT(_xlfn.ISFORMULA('F2-1 Arena'!$G$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-1 Arena'!$G$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-1 Arena'!$G$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('F2-1 Arena'!$G$6),'F2-1 Arena'!$G$6=(Key!$C$18="TRUE")),FALSE))),"✘ TRY AGAIN","✔ CLEAR"))))</f>
@@ -9040,13 +9052,13 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F2-1 Arena'!$G$7),"",IF(NOT(_xlfn.ISFORMULA('F2-1 Arena'!$G$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-1 Arena'!$G$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-1 Arena'!$G$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('F2-1 Arena'!$G$7),'F2-1 Arena'!$G$7=(Key!$C$19="TRUE")),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("&lt;&gt;",_xlfn.FORMULATEXT('F2-1 Arena'!$G$7))),"✔ CLEAR","✘ CLOSE · your formula needs &lt;&gt;")))))</f>
@@ -9064,13 +9076,13 @@
     </row>
     <row r="38" spans="1:7" ht="51.25" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F2-1 Arena'!$G$8),"",IF(NOT(_xlfn.ISFORMULA('F2-1 Arena'!$G$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-1 Arena'!$G$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-1 Arena'!$G$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('F2-1 Arena'!$G$8),'F2-1 Arena'!$G$8=(Key!$C$20="TRUE")),FALSE))),"✘ TRY AGAIN","✔ CLEAR"))))</f>
@@ -9417,7 +9429,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9428,7 +9440,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9480,10 +9492,10 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="67" customHeight="1">
@@ -9491,7 +9503,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>118</v>
@@ -9502,7 +9514,7 @@
         <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>124</v>
@@ -9547,7 +9559,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -9569,7 +9581,7 @@
         <v>55</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -9591,7 +9603,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -9613,7 +9625,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -9635,7 +9647,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -9657,7 +9669,7 @@
         <v>75</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -9679,7 +9691,7 @@
         <v>80</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -9701,7 +9713,7 @@
         <v>85</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -9723,7 +9735,7 @@
         <v>94</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -9745,7 +9757,7 @@
         <v>108</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -9801,7 +9813,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -9823,7 +9835,7 @@
         <v>120</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -9845,7 +9857,7 @@
         <v>125</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -9875,7 +9887,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -9906,7 +9918,7 @@
         <v>130</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -9928,7 +9940,7 @@
         <v>132</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -9950,7 +9962,7 @@
         <v>138</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -9969,13 +9981,13 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(COUNTA('F2-2 Arena'!$F$6,'F2-2 Arena'!$F$7,'F2-2 Arena'!$F$8,'F2-2 Arena'!$F$9,'F2-2 Arena'!$F$10,'F2-2 Arena'!$F$11,'F2-2 Arena'!$F$12,'F2-2 Arena'!$F$13,'F2-2 Arena'!$F$14,'F2-2 Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$6)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$7)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$8)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$9)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$10)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$11)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$12)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$13)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$14)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-2 Arena'!$F$6),ISERROR('F2-2 Arena'!$F$7),ISERROR('F2-2 Arena'!$F$8),ISERROR('F2-2 Arena'!$F$9),ISERROR('F2-2 Arena'!$F$10),ISERROR('F2-2 Arena'!$F$11),ISERROR('F2-2 Arena'!$F$12),ISERROR('F2-2 Arena'!$F$13),ISERROR('F2-2 Arena'!$F$14),ISERROR('F2-2 Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-2 Arena'!$F$6),'F2-2 Arena'!$F$6=Key!$E$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$7),'F2-2 Arena'!$F$7=Key!$F$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$8),'F2-2 Arena'!$F$8=Key!$G$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$9),'F2-2 Arena'!$F$9=Key!$H$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$10),'F2-2 Arena'!$F$10=Key!$I$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$11),'F2-2 Arena'!$F$11=Key!$J$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$12),'F2-2 Arena'!$F$12=Key!$K$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$13),'F2-2 Arena'!$F$13=Key!$L$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$14),'F2-2 Arena'!$F$14=Key!$M$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$15),'F2-2 Arena'!$F$15=Key!$N$37),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-2 Arena'!$F$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF")))))</f>
@@ -9993,13 +10005,13 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(COUNTA('F2-2 Arena'!$G$6,'F2-2 Arena'!$G$7,'F2-2 Arena'!$G$8,'F2-2 Arena'!$G$9,'F2-2 Arena'!$G$10,'F2-2 Arena'!$G$11,'F2-2 Arena'!$G$12,'F2-2 Arena'!$G$13,'F2-2 Arena'!$G$14,'F2-2 Arena'!$G$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$6)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$7)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$8)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$9)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$10)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$11)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$12)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$13)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$14)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-2 Arena'!$G$6),ISERROR('F2-2 Arena'!$G$7),ISERROR('F2-2 Arena'!$G$8),ISERROR('F2-2 Arena'!$G$9),ISERROR('F2-2 Arena'!$G$10),ISERROR('F2-2 Arena'!$G$11),ISERROR('F2-2 Arena'!$G$12),ISERROR('F2-2 Arena'!$G$13),ISERROR('F2-2 Arena'!$G$14),ISERROR('F2-2 Arena'!$G$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$6),ABS('F2-2 Arena'!$G$6-Key!$E$38)&lt;=1E-9*MAX(1,ABS(Key!$E$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$7),ABS('F2-2 Arena'!$G$7-Key!$F$38)&lt;=1E-9*MAX(1,ABS(Key!$F$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$8),ABS('F2-2 Arena'!$G$8-Key!$G$38)&lt;=1E-9*MAX(1,ABS(Key!$G$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$9),ABS('F2-2 Arena'!$G$9-Key!$H$38)&lt;=1E-9*MAX(1,ABS(Key!$H$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$10),ABS('F2-2 Arena'!$G$10-Key!$I$38)&lt;=1E-9*MAX(1,ABS(Key!$I$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$11),ABS('F2-2 Arena'!$G$11-Key!$J$38)&lt;=1E-9*MAX(1,ABS(Key!$J$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$12),ABS('F2-2 Arena'!$G$12-Key!$K$38)&lt;=1E-9*MAX(1,ABS(Key!$K$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$13),ABS('F2-2 Arena'!$G$13-Key!$L$38)&lt;=1E-9*MAX(1,ABS(Key!$L$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$14),ABS('F2-2 Arena'!$G$14-Key!$M$38)&lt;=1E-9*MAX(1,ABS(Key!$M$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$15),ABS('F2-2 Arena'!$G$15-Key!$N$38)&lt;=1E-9*MAX(1,ABS(Key!$N$38))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-2 Arena'!$G$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF")))))</f>
@@ -10017,13 +10029,13 @@
     </row>
     <row r="38" spans="1:7" ht="51.25" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F2-2 Arena'!$I$6),"",IF(NOT(_xlfn.ISFORMULA('F2-2 Arena'!$I$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-2 Arena'!$I$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-2 Arena'!$I$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F2-2 Arena'!$I$6),'F2-2 Arena'!$I$6=Key!$C$39),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-2 Arena'!$I$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF")))))</f>
@@ -10157,7 +10169,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -10170,10 +10182,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -10193,13 +10205,13 @@
         <v>44</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -10391,7 +10403,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10402,7 +10414,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -10454,10 +10466,10 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="35.5" customHeight="1">
@@ -10465,10 +10477,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.5" customHeight="1">
@@ -10476,10 +10488,10 @@
         <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1">
@@ -10521,7 +10533,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -10543,7 +10555,7 @@
         <v>55</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -10565,7 +10577,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -10587,7 +10599,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -10609,7 +10621,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -10631,7 +10643,7 @@
         <v>75</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -10653,7 +10665,7 @@
         <v>80</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -10675,7 +10687,7 @@
         <v>85</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -10697,7 +10709,7 @@
         <v>94</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -10719,7 +10731,7 @@
         <v>108</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -10775,7 +10787,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -10797,7 +10809,7 @@
         <v>120</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -10819,7 +10831,7 @@
         <v>125</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -10849,7 +10861,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -10880,7 +10892,7 @@
         <v>130</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -10902,7 +10914,7 @@
         <v>132</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -10924,7 +10936,7 @@
         <v>138</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -10943,13 +10955,13 @@
     </row>
     <row r="36" spans="1:7" ht="51.25" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(COUNTA('F2-3 Arena'!$F$6,'F2-3 Arena'!$F$7,'F2-3 Arena'!$F$8,'F2-3 Arena'!$F$9,'F2-3 Arena'!$F$10,'F2-3 Arena'!$F$11,'F2-3 Arena'!$F$12,'F2-3 Arena'!$F$13,'F2-3 Arena'!$F$14,'F2-3 Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$6)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$7)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$8)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$9)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$10)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$11)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$12)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$13)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$14)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-3 Arena'!$F$6),ISERROR('F2-3 Arena'!$F$7),ISERROR('F2-3 Arena'!$F$8),ISERROR('F2-3 Arena'!$F$9),ISERROR('F2-3 Arena'!$F$10),ISERROR('F2-3 Arena'!$F$11),ISERROR('F2-3 Arena'!$F$12),ISERROR('F2-3 Arena'!$F$13),ISERROR('F2-3 Arena'!$F$14),ISERROR('F2-3 Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-3 Arena'!$F$6),'F2-3 Arena'!$F$6=Key!$E$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$7),'F2-3 Arena'!$F$7=Key!$F$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$8),'F2-3 Arena'!$F$8=Key!$G$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$9),'F2-3 Arena'!$F$9=Key!$H$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$10),'F2-3 Arena'!$F$10=Key!$I$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$11),'F2-3 Arena'!$F$11=Key!$J$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$12),'F2-3 Arena'!$F$12=Key!$K$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$13),'F2-3 Arena'!$F$13=Key!$L$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$14),'F2-3 Arena'!$F$14=Key!$M$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$15),'F2-3 Arena'!$F$15=Key!$N$56),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-3 Arena'!$F$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use AND")))))</f>
@@ -10967,13 +10979,13 @@
     </row>
     <row r="37" spans="1:7" ht="51.25" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(COUNTA('F2-3 Arena'!$G$6,'F2-3 Arena'!$G$7,'F2-3 Arena'!$G$8,'F2-3 Arena'!$G$9,'F2-3 Arena'!$G$10,'F2-3 Arena'!$G$11,'F2-3 Arena'!$G$12,'F2-3 Arena'!$G$13,'F2-3 Arena'!$G$14,'F2-3 Arena'!$G$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$6)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$7)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$8)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$9)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$10)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$11)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$12)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$13)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$14)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-3 Arena'!$G$6),ISERROR('F2-3 Arena'!$G$7),ISERROR('F2-3 Arena'!$G$8),ISERROR('F2-3 Arena'!$G$9),ISERROR('F2-3 Arena'!$G$10),ISERROR('F2-3 Arena'!$G$11),ISERROR('F2-3 Arena'!$G$12),ISERROR('F2-3 Arena'!$G$13),ISERROR('F2-3 Arena'!$G$14),ISERROR('F2-3 Arena'!$G$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-3 Arena'!$G$6),'F2-3 Arena'!$G$6=Key!$E$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$7),'F2-3 Arena'!$G$7=Key!$F$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$8),'F2-3 Arena'!$G$8=Key!$G$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$9),'F2-3 Arena'!$G$9=Key!$H$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$10),'F2-3 Arena'!$G$10=Key!$I$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$11),'F2-3 Arena'!$G$11=Key!$J$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$12),'F2-3 Arena'!$G$12=Key!$K$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$13),'F2-3 Arena'!$G$13=Key!$L$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$14),'F2-3 Arena'!$G$14=Key!$M$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$15),'F2-3 Arena'!$G$15=Key!$N$57),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"OR"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-3 Arena'!$G$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use OR")))))</f>
@@ -10991,13 +11003,13 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F2-3 Arena'!$I$6),"",IF(NOT(_xlfn.ISFORMULA('F2-3 Arena'!$I$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-3 Arena'!$I$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-3 Arena'!$I$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('F2-3 Arena'!$I$6),'F2-3 Arena'!$I$6=(Key!$C$58="TRUE")),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"NOT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-3 Arena'!$I$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use NOT")))))</f>
@@ -11131,7 +11143,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -11144,10 +11156,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -11164,13 +11176,13 @@
         <v>12</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -11362,7 +11374,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11373,7 +11385,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -11425,7 +11437,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>119</v>
@@ -11436,10 +11448,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="51.25" customHeight="1">
@@ -11447,7 +11459,7 @@
         <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>113</v>
@@ -11492,7 +11504,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -11514,7 +11526,7 @@
         <v>55</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -11536,7 +11548,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -11558,7 +11570,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -11580,7 +11592,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -11602,7 +11614,7 @@
         <v>75</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -11624,7 +11636,7 @@
         <v>80</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -11646,7 +11658,7 @@
         <v>85</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -11668,7 +11680,7 @@
         <v>94</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -11690,7 +11702,7 @@
         <v>108</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -11746,7 +11758,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -11768,7 +11780,7 @@
         <v>120</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -11790,7 +11802,7 @@
         <v>125</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -11820,7 +11832,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -11851,7 +11863,7 @@
         <v>130</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -11873,7 +11885,7 @@
         <v>132</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -11895,7 +11907,7 @@
         <v>138</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -11914,13 +11926,13 @@
     </row>
     <row r="36" spans="1:7" ht="51.25" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(COUNTA('F2-4 Arena'!$F$6,'F2-4 Arena'!$F$7,'F2-4 Arena'!$F$8,'F2-4 Arena'!$F$9,'F2-4 Arena'!$F$10,'F2-4 Arena'!$F$11,'F2-4 Arena'!$F$12,'F2-4 Arena'!$F$13,'F2-4 Arena'!$F$14,'F2-4 Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$6)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$7)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$8)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$9)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$10)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$11)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$12)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$13)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$14)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-4 Arena'!$F$6),ISERROR('F2-4 Arena'!$F$7),ISERROR('F2-4 Arena'!$F$8),ISERROR('F2-4 Arena'!$F$9),ISERROR('F2-4 Arena'!$F$10),ISERROR('F2-4 Arena'!$F$11),ISERROR('F2-4 Arena'!$F$12),ISERROR('F2-4 Arena'!$F$13),ISERROR('F2-4 Arena'!$F$14),ISERROR('F2-4 Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-4 Arena'!$F$6),'F2-4 Arena'!$F$6=Key!$E$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$7),'F2-4 Arena'!$F$7=Key!$F$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$8),'F2-4 Arena'!$F$8=Key!$G$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$9),'F2-4 Arena'!$F$9=Key!$H$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$10),'F2-4 Arena'!$F$10=Key!$I$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$11),'F2-4 Arena'!$F$11=Key!$J$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$12),'F2-4 Arena'!$F$12=Key!$K$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$13),'F2-4 Arena'!$F$13=Key!$L$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$14),'F2-4 Arena'!$F$14=Key!$M$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$15),'F2-4 Arena'!$F$15=Key!$N$75),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-4 Arena'!$F$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF")))))</f>
@@ -11938,13 +11950,13 @@
     </row>
     <row r="37" spans="1:7" ht="51.25" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(COUNTA('F2-4 Arena'!$G$6,'F2-4 Arena'!$G$7,'F2-4 Arena'!$G$8,'F2-4 Arena'!$G$9,'F2-4 Arena'!$G$10,'F2-4 Arena'!$G$11,'F2-4 Arena'!$G$12,'F2-4 Arena'!$G$13,'F2-4 Arena'!$G$14,'F2-4 Arena'!$G$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$6)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$7)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$8)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$9)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$10)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$11)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$12)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$13)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$14)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-4 Arena'!$G$6),ISERROR('F2-4 Arena'!$G$7),ISERROR('F2-4 Arena'!$G$8),ISERROR('F2-4 Arena'!$G$9),ISERROR('F2-4 Arena'!$G$10),ISERROR('F2-4 Arena'!$G$11),ISERROR('F2-4 Arena'!$G$12),ISERROR('F2-4 Arena'!$G$13),ISERROR('F2-4 Arena'!$G$14),ISERROR('F2-4 Arena'!$G$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-4 Arena'!$G$6),'F2-4 Arena'!$G$6=Key!$E$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$7),'F2-4 Arena'!$G$7=Key!$F$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$8),'F2-4 Arena'!$G$8=Key!$G$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$9),'F2-4 Arena'!$G$9=Key!$H$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$10),'F2-4 Arena'!$G$10=Key!$I$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$11),'F2-4 Arena'!$G$11=Key!$J$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$12),'F2-4 Arena'!$G$12=Key!$K$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$13),'F2-4 Arena'!$G$13=Key!$L$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$14),'F2-4 Arena'!$G$14=Key!$M$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$15),'F2-4 Arena'!$G$15=Key!$N$76),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-4 Arena'!$G$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFS")))))</f>
@@ -11962,10 +11974,10 @@
     </row>
     <row r="38" spans="1:7" ht="51.25" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -12100,7 +12112,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -12113,10 +12125,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -12133,13 +12145,13 @@
         <v>12</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -12158,7 +12170,7 @@
       <c r="F6" s="28"/>
       <c r="G6" s="28"/>
       <c r="I6" s="5" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:9">

--- a/workbooks/04 Formulas 2 - Logic.xlsx
+++ b/workbooks/04 Formulas 2 - Logic.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="710">
   <si>
     <t>Challenge</t>
   </si>
@@ -562,10 +562,19 @@
     <t>"</t>
   </si>
   <si>
+    <t>DOUBLEQUOTE</t>
+  </si>
+  <si>
     <t>DOUBLEQUOTES</t>
   </si>
   <si>
+    <t>QUOTATIONMARK</t>
+  </si>
+  <si>
     <t>QUOTATIONMARKS</t>
+  </si>
+  <si>
+    <t>QUOTE</t>
   </si>
   <si>
     <t>QUOTES</t>
@@ -1678,7 +1687,22 @@
     <t>F2-4 Multi-Level C3</t>
   </si>
   <si>
+    <t>=TRUE</t>
+  </si>
+  <si>
+    <t>=TRUE(</t>
+  </si>
+  <si>
+    <t>=TRUE()</t>
+  </si>
+  <si>
     <t>TRUE</t>
+  </si>
+  <si>
+    <t>TRUE(</t>
+  </si>
+  <si>
+    <t>TRUE()</t>
   </si>
   <si>
     <t>In IFS, what do you put as the last test to catch all remaining cases?</t>
@@ -2568,7 +2592,7 @@
     <t>NEXT UP</t>
   </si>
   <si>
-    <t>Replay a stage: select its yellow answer cells and press Delete. Undo an arena drill with Ctrl+Z.</t>
+    <t>Replay a stage: select a run of its yellow cells (Ctrl+click to add more), then press Delete. Undo an arena drill with Ctrl+Z.</t>
   </si>
   <si>
     <t>CHEAT CODES ▸ LOGIC</t>
@@ -3362,7 +3386,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3372,12 +3396,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3387,32 +3411,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3422,7 +3446,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
@@ -3431,21 +3455,21 @@
         <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F2-1 True or False'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3460,15 +3484,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F2-2 Fork in the Road'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3483,15 +3507,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F2-3 Combo Moves'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3506,15 +3530,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F2-4 Multi-Level'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3529,15 +3553,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM('F2-5 Error Shield'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3552,15 +3576,15 @@
         <v>NEW</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="C18" s="9" cm="1" t="str">
         <f t="array" ref="C18">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3575,12 +3599,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">(SUM('F2-1 True or False'!$G$13:$G$38)+SUM('F2-2 Fork in the Road'!$G$13:$G$38)+SUM('F2-3 Combo Moves'!$G$13:$G$38)+SUM('F2-4 Multi-Level'!$G$13:$G$38)+SUM('F2-5 Error Shield'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 1140"</f>
@@ -3589,19 +3613,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">_xlfn.LET(_xlpm.p,(SUM('F2-1 True or False'!$G$13:$G$38)+SUM('F2-2 Fork in the Road'!$G$13:$G$38)+SUM('F2-3 Combo Moves'!$G$13:$G$38)+SUM('F2-4 Multi-Level'!$G$13:$G$38)+SUM('F2-5 Error Shield'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))/1140,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3610,16 +3634,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="7" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="B23" s="12" cm="1" t="str">
-        <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
+        <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Start!$E$18="DEFEATED","All clear! Aim for rank S","the Boss"))</f>
         <v>F2-1 True or False</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="13" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -3657,7 +3681,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3668,7 +3692,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3720,10 +3744,10 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="51.25" customHeight="1">
@@ -3731,10 +3755,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.5" customHeight="1">
@@ -3742,21 +3766,21 @@
         <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="51.25" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
@@ -3798,7 +3822,7 @@
         <v>50</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -3820,7 +3844,7 @@
         <v>55</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -3842,11 +3866,11 @@
         <v>60</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
-        <f t="array" ref="D16">IFERROR(_xlfn.LET(_xlpm.a,'F2-5 Error Shield'!$C$16,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$80:$E$80),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D16">IFERROR(_xlfn.LET(_xlpm.a,'F2-5 Error Shield'!$C$16,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$80:$J$80),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E16" s="22"/>
@@ -3864,7 +3888,7 @@
         <v>65</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -3886,7 +3910,7 @@
         <v>70</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -3908,11 +3932,11 @@
         <v>75</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
-        <f t="array" ref="D19">IFERROR(_xlfn.LET(_xlpm.a,'F2-5 Error Shield'!$C$19,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$83:$H$83),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D19">IFERROR(_xlfn.LET(_xlpm.a,'F2-5 Error Shield'!$C$19,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$83:$K$83),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E19" s="22"/>
@@ -3930,7 +3954,7 @@
         <v>80</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -3952,7 +3976,7 @@
         <v>85</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -3974,7 +3998,7 @@
         <v>94</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -3996,7 +4020,7 @@
         <v>108</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -4052,7 +4076,7 @@
         <v>114</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -4074,7 +4098,7 @@
         <v>120</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -4096,7 +4120,7 @@
         <v>125</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -4115,10 +4139,10 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -4148,7 +4172,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="11" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -4179,7 +4203,7 @@
         <v>130</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -4201,7 +4225,7 @@
         <v>132</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -4220,10 +4244,10 @@
     </row>
     <row r="37" spans="1:7" ht="19.75" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -4242,10 +4266,10 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -4264,13 +4288,13 @@
     </row>
     <row r="39" spans="1:7" ht="51.25" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(COUNTA('F2-5 Arena'!$E$6,'F2-5 Arena'!$E$7,'F2-5 Arena'!$E$8,'F2-5 Arena'!$E$9,'F2-5 Arena'!$E$10,'F2-5 Arena'!$E$11)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$6)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$7)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$8)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$9)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$10)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$11))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-5 Arena'!$E$6),ISERROR('F2-5 Arena'!$E$7),ISERROR('F2-5 Arena'!$E$8),ISERROR('F2-5 Arena'!$E$9),ISERROR('F2-5 Arena'!$E$10),ISERROR('F2-5 Arena'!$E$11)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$6),ABS('F2-5 Arena'!$E$6-Key!$E$96)&lt;=1E-9*MAX(1,ABS(Key!$E$96))),FALSE),IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$7),ABS('F2-5 Arena'!$E$7-Key!$F$96)&lt;=1E-9*MAX(1,ABS(Key!$F$96))),FALSE),IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$8),ABS('F2-5 Arena'!$E$8-Key!$G$96)&lt;=1E-9*MAX(1,ABS(Key!$G$96))),FALSE),IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$9),ABS('F2-5 Arena'!$E$9-Key!$H$96)&lt;=1E-9*MAX(1,ABS(Key!$H$96))),FALSE),IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$10),ABS('F2-5 Arena'!$E$10-Key!$I$96)&lt;=1E-9*MAX(1,ABS(Key!$I$96))),FALSE),IFERROR(AND(ISNUMBER('F2-5 Arena'!$E$11),ABS('F2-5 Arena'!$E$11-Key!$J$96)&lt;=1E-9*MAX(1,ABS(Key!$J$96))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFERROR"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-5 Arena'!$E$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFERROR")))))</f>
@@ -4288,13 +4312,13 @@
     </row>
     <row r="40" spans="1:7" ht="35.5" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="D40" s="21" cm="1" t="str">
         <f t="array" ref="D40">IF(ISBLANK('F2-5 Arena'!$F$14),"",IF(NOT(_xlfn.ISFORMULA('F2-5 Arena'!$F$14)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-5 Arena'!$F$14),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-5 Arena'!$F$14),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F2-5 Arena'!$F$14),'F2-5 Arena'!$F$14=Key!$C$97),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFNA"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-5 Arena'!$F$14)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFNA")))))</f>
@@ -4312,13 +4336,13 @@
     </row>
     <row r="41" spans="1:7" ht="51.25" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D41" s="21" cm="1" t="str">
         <f t="array" ref="D41">IF(COUNTA('F2-5 Arena'!$C$17,'F2-5 Arena'!$C$18,'F2-5 Arena'!$C$19,'F2-5 Arena'!$C$20,'F2-5 Arena'!$C$21)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-5 Arena'!$C$17)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$C$18)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$C$19)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$C$20)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$C$21))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-5 Arena'!$C$17),ISERROR('F2-5 Arena'!$C$18),ISERROR('F2-5 Arena'!$C$19),ISERROR('F2-5 Arena'!$C$20),ISERROR('F2-5 Arena'!$C$21)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-5 Arena'!$C$17),'F2-5 Arena'!$C$17=Key!$E$98),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$C$18),'F2-5 Arena'!$C$18=Key!$F$98),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$C$19),'F2-5 Arena'!$C$19=Key!$G$98),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$C$20),'F2-5 Arena'!$C$20=Key!$H$98),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$C$21),'F2-5 Arena'!$C$21=Key!$I$98),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ISBLANK"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-5 Arena'!$C$17)))))),"✔ CLEAR","✘ CLOSE · right value, but use ISBLANK")))))</f>
@@ -4336,13 +4360,13 @@
     </row>
     <row r="42" spans="1:7" ht="51.25" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(COUNTA('F2-5 Arena'!$E$23,'F2-5 Arena'!$E$24,'F2-5 Arena'!$E$25,'F2-5 Arena'!$E$26,'F2-5 Arena'!$E$27)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$23)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$24)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$25)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$26)),NOT(_xlfn.ISFORMULA('F2-5 Arena'!$E$27))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-5 Arena'!$E$23),ISERROR('F2-5 Arena'!$E$24),ISERROR('F2-5 Arena'!$E$25),ISERROR('F2-5 Arena'!$E$26),ISERROR('F2-5 Arena'!$E$27)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-5 Arena'!$E$23),'F2-5 Arena'!$E$23=Key!$E$99),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$E$24),'F2-5 Arena'!$E$24=Key!$F$99),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$E$25),'F2-5 Arena'!$E$25=Key!$G$99),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$E$26),'F2-5 Arena'!$E$26=Key!$H$99),FALSE),IFERROR(AND(ISTEXT('F2-5 Arena'!$E$27),'F2-5 Arena'!$E$27=Key!$I$99),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ISNUMBER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-5 Arena'!$E$23)))))),"✔ CLEAR","✘ CLOSE · right value, but use ISNUMBER")))))</f>
@@ -4488,7 +4512,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4501,29 +4525,29 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="27" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="5" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C6" s="5">
         <v>120</v>
@@ -4535,7 +4559,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="5" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C7" s="5">
         <v>90</v>
@@ -4547,7 +4571,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="5" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C8" s="5">
         <v>60</v>
@@ -4559,7 +4583,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="5" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
@@ -4571,7 +4595,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="5" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C10" s="5">
         <v>45</v>
@@ -4583,7 +4607,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="B11" s="5" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C11" s="5">
         <v>30</v>
@@ -4595,14 +4619,14 @@
     </row>
     <row r="14" spans="1:6">
       <c r="B14" s="7" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="D14" s="5" cm="1" t="str">
         <f t="array" ref="D14">NA()</f>
         <v>#N/A</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="F14" s="28"/>
     </row>
@@ -4611,7 +4635,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -4640,10 +4664,10 @@
     </row>
     <row r="22" spans="2:5">
       <c r="D22" s="27" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -4654,7 +4678,7 @@
     </row>
     <row r="24" spans="2:5">
       <c r="D24" s="5" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="E24" s="28"/>
     </row>
@@ -4666,7 +4690,7 @@
     </row>
     <row r="26" spans="2:5">
       <c r="D26" s="5" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="E26" s="28"/>
     </row>
@@ -4704,7 +4728,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4715,7 +4739,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -4734,7 +4758,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4745,19 +4769,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="C6" s="29"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C8" s="30" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -4766,7 +4790,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="C9" s="30">
         <v>15</v>
@@ -4774,7 +4798,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F2-1 True or False'!$G$13:$G$38)&gt;=190*0.5,SUM('F2-2 Fork in the Road'!$G$13:$G$38)&gt;=190*0.5,SUM('F2-3 Combo Moves'!$G$13:$G$38)&gt;=190*0.5,SUM('F2-4 Multi-Level'!$G$13:$G$38)&gt;=190*0.5,SUM('F2-5 Error Shield'!$G$14:$G$42)&gt;=220*0.5),"OPEN","LOCKED")</f>
@@ -4787,7 +4811,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4821,7 +4845,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="B14" s="31" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which function replaces any error with your own value?  (from F2-5 Error Shield)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4844,7 +4868,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="B15" s="31" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","Which function replaces only the #N/A error?  (from F2-5 Error Shield)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4867,7 +4891,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="B16" s="31" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which function is TRUE when a cell is empty?  (from F2-5 Error Shield)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4890,7 +4914,7 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="B17" s="31" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","Which function is TRUE when a value is a number?  (from F2-5 Error Shield)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4913,7 +4937,7 @@
     </row>
     <row r="18" spans="1:7" ht="51.25" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B18" s="31" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which function returns one value when a test is TRUE and another when FALSE?  (from F2-2 Fork in the Road)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4936,7 +4960,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="B19" s="31" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","In =IF"&amp;"(B2&gt;100,B2*0.9,B2), what is returned when B2 is 50?  (from F2-2 Fork in the Road)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4959,7 +4983,7 @@
     </row>
     <row r="20" spans="1:7" ht="51.25" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="B20" s="31" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","What do you type in a formula for an empty, blank-looking result?  (from F2-2 Fork in the Road)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4982,7 +5006,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="B21" s="31" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which function counts every non-empty cell?  (from F1-2 Big Six)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5005,7 +5029,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -5016,7 +5040,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5044,17 +5068,17 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="B26" s="31" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In F6 return ""Pass"" for a Score of 60 or more, otherwise ""Fail"". Fill down to F15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
-        <f t="array" ref="D26">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$F$6,'Boss Arena'!$F$7,'Boss Arena'!$F$8,'Boss Arena'!$F$9,'Boss Arena'!$F$10,'Boss Arena'!$F$11,'Boss Arena'!$F$12,'Boss Arena'!$F$13,'Boss Arena'!$F$14,'Boss Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$F$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$F$6),ISERROR('Boss Arena'!$F$7),ISERROR('Boss Arena'!$F$8),ISERROR('Boss Arena'!$F$9),ISERROR('Boss Arena'!$F$10),ISERROR('Boss Arena'!$F$11),ISERROR('Boss Arena'!$F$12),ISERROR('Boss Arena'!$F$13),ISERROR('Boss Arena'!$F$14),ISERROR('Boss Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$F$6),'Boss Arena'!$F$6=Key!$E$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$7),'Boss Arena'!$F$7=Key!$F$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$8),'Boss Arena'!$F$8=Key!$G$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$9),'Boss Arena'!$F$9=Key!$H$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$10),'Boss Arena'!$F$10=Key!$I$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$11),'Boss Arena'!$F$11=Key!$J$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$12),'Boss Arena'!$F$12=Key!$K$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$13),'Boss Arena'!$F$13=Key!$L$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$14),'Boss Arena'!$F$14=Key!$M$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$15),'Boss Arena'!$F$15=Key!$N$108),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$F$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF"))))),"LOCKED")</f>
+        <f t="array" ref="D26">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$F$6,'Boss Arena'!$F$7,'Boss Arena'!$F$8,'Boss Arena'!$F$9,'Boss Arena'!$F$10,'Boss Arena'!$F$11,'Boss Arena'!$F$12,'Boss Arena'!$F$13,'Boss Arena'!$F$14,'Boss Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$F$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$F$6),ISERROR('Boss Arena'!$F$7),ISERROR('Boss Arena'!$F$8),ISERROR('Boss Arena'!$F$9),ISERROR('Boss Arena'!$F$10),ISERROR('Boss Arena'!$F$11),ISERROR('Boss Arena'!$F$12),ISERROR('Boss Arena'!$F$13),ISERROR('Boss Arena'!$F$14),ISERROR('Boss Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$F$6),'Boss Arena'!$F$6=Key!$E$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$7),'Boss Arena'!$F$7=Key!$F$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$8),'Boss Arena'!$F$8=Key!$G$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$9),'Boss Arena'!$F$9=Key!$H$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$10),'Boss Arena'!$F$10=Key!$I$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$11),'Boss Arena'!$F$11=Key!$J$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$12),'Boss Arena'!$F$12=Key!$K$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$13),'Boss Arena'!$F$13=Key!$L$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$14),'Boss Arena'!$F$14=Key!$M$108),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$F$15),'Boss Arena'!$F$15=Key!$N$108),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$F$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$F$6))))))),"✔ CLEAR","✘ CLOSE · right value, but use IF/IFS"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E26" s="22"/>
@@ -5069,14 +5093,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="B27" s="31" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In G6 return ""Yes"" when Age is 18+ AND Score is 70+, otherwise ""No"". Fill down to G15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$G$6,'Boss Arena'!$G$7,'Boss Arena'!$G$8,'Boss Arena'!$G$9,'Boss Arena'!$G$10,'Boss Arena'!$G$11,'Boss Arena'!$G$12,'Boss Arena'!$G$13,'Boss Arena'!$G$14,'Boss Arena'!$G$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$G$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$G$6),ISERROR('Boss Arena'!$G$7),ISERROR('Boss Arena'!$G$8),ISERROR('Boss Arena'!$G$9),ISERROR('Boss Arena'!$G$10),ISERROR('Boss Arena'!$G$11),ISERROR('Boss Arena'!$G$12),ISERROR('Boss Arena'!$G$13),ISERROR('Boss Arena'!$G$14),ISERROR('Boss Arena'!$G$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$G$6),'Boss Arena'!$G$6=Key!$E$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$7),'Boss Arena'!$G$7=Key!$F$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$8),'Boss Arena'!$G$8=Key!$G$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$9),'Boss Arena'!$G$9=Key!$H$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$10),'Boss Arena'!$G$10=Key!$I$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$11),'Boss Arena'!$G$11=Key!$J$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$12),'Boss Arena'!$G$12=Key!$K$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$13),'Boss Arena'!$G$13=Key!$L$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$14),'Boss Arena'!$G$14=Key!$M$109),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$G$15),'Boss Arena'!$G$15=Key!$N$109),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$G$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use AND"))))),"LOCKED")</f>
@@ -5094,14 +5118,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="B28" s="31" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In H6 return ""Star"" when Score is 95+ OR Age is 40+, otherwise ""No"". Fill down to H15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$H$6,'Boss Arena'!$H$7,'Boss Arena'!$H$8,'Boss Arena'!$H$9,'Boss Arena'!$H$10,'Boss Arena'!$H$11,'Boss Arena'!$H$12,'Boss Arena'!$H$13,'Boss Arena'!$H$14,'Boss Arena'!$H$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$H$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$H$6),ISERROR('Boss Arena'!$H$7),ISERROR('Boss Arena'!$H$8),ISERROR('Boss Arena'!$H$9),ISERROR('Boss Arena'!$H$10),ISERROR('Boss Arena'!$H$11),ISERROR('Boss Arena'!$H$12),ISERROR('Boss Arena'!$H$13),ISERROR('Boss Arena'!$H$14),ISERROR('Boss Arena'!$H$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$H$6),'Boss Arena'!$H$6=Key!$E$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$7),'Boss Arena'!$H$7=Key!$F$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$8),'Boss Arena'!$H$8=Key!$G$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$9),'Boss Arena'!$H$9=Key!$H$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$10),'Boss Arena'!$H$10=Key!$I$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$11),'Boss Arena'!$H$11=Key!$J$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$12),'Boss Arena'!$H$12=Key!$K$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$13),'Boss Arena'!$H$13=Key!$L$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$14),'Boss Arena'!$H$14=Key!$M$110),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$15),'Boss Arena'!$H$15=Key!$N$110),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"OR"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$H$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use OR"))))),"LOCKED")</f>
@@ -5119,14 +5143,14 @@
     </row>
     <row r="29" spans="1:7" ht="51.25" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="B29" s="31" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In I6 use IFS: ""Gold"" for 90+, ""Silver"" for 75+, ""Bronze"" for 60+, otherwise ""None"". Fill down.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$I$6,'Boss Arena'!$I$7,'Boss Arena'!$I$8,'Boss Arena'!$I$9,'Boss Arena'!$I$10,'Boss Arena'!$I$11,'Boss Arena'!$I$12,'Boss Arena'!$I$13,'Boss Arena'!$I$14,'Boss Arena'!$I$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$I$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$I$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$I$6),ISERROR('Boss Arena'!$I$7),ISERROR('Boss Arena'!$I$8),ISERROR('Boss Arena'!$I$9),ISERROR('Boss Arena'!$I$10),ISERROR('Boss Arena'!$I$11),ISERROR('Boss Arena'!$I$12),ISERROR('Boss Arena'!$I$13),ISERROR('Boss Arena'!$I$14),ISERROR('Boss Arena'!$I$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$I$6),'Boss Arena'!$I$6=Key!$E$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$7),'Boss Arena'!$I$7=Key!$F$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$8),'Boss Arena'!$I$8=Key!$G$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$9),'Boss Arena'!$I$9=Key!$H$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$10),'Boss Arena'!$I$10=Key!$I$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$11),'Boss Arena'!$I$11=Key!$J$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$12),'Boss Arena'!$I$12=Key!$K$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$13),'Boss Arena'!$I$13=Key!$L$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$14),'Boss Arena'!$I$14=Key!$M$111),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$I$15),'Boss Arena'!$I$15=Key!$N$111),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$I$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFS"))))),"LOCKED")</f>
@@ -5144,17 +5168,17 @@
     </row>
     <row r="30" spans="1:7" ht="51.25" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="B30" s="31" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In J6 return ""VIP"" for Score 80+ AND Age 18+, otherwise ""Member"" for Score 60+, otherwise ""Guest"". Fill down to J15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
-        <f t="array" ref="D30">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$J$6,'Boss Arena'!$J$7,'Boss Arena'!$J$8,'Boss Arena'!$J$9,'Boss Arena'!$J$10,'Boss Arena'!$J$11,'Boss Arena'!$J$12,'Boss Arena'!$J$13,'Boss Arena'!$J$14,'Boss Arena'!$J$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$J$6),ISERROR('Boss Arena'!$J$7),ISERROR('Boss Arena'!$J$8),ISERROR('Boss Arena'!$J$9),ISERROR('Boss Arena'!$J$10),ISERROR('Boss Arena'!$J$11),ISERROR('Boss Arena'!$J$12),ISERROR('Boss Arena'!$J$13),ISERROR('Boss Arena'!$J$14),ISERROR('Boss Arena'!$J$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$6),'Boss Arena'!$J$6=Key!$E$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$7),'Boss Arena'!$J$7=Key!$F$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$8),'Boss Arena'!$J$8=Key!$G$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$9),'Boss Arena'!$J$9=Key!$H$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$10),'Boss Arena'!$J$10=Key!$I$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$11),'Boss Arena'!$J$11=Key!$J$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$12),'Boss Arena'!$J$12=Key!$K$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$13),'Boss Arena'!$J$13=Key!$L$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$14),'Boss Arena'!$J$14=Key!$M$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$15),'Boss Arena'!$J$15=Key!$N$112),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF and AND"))))),"LOCKED")</f>
+        <f t="array" ref="D30">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$J$6,'Boss Arena'!$J$7,'Boss Arena'!$J$8,'Boss Arena'!$J$9,'Boss Arena'!$J$10,'Boss Arena'!$J$11,'Boss Arena'!$J$12,'Boss Arena'!$J$13,'Boss Arena'!$J$14,'Boss Arena'!$J$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$J$6),ISERROR('Boss Arena'!$J$7),ISERROR('Boss Arena'!$J$8),ISERROR('Boss Arena'!$J$9),ISERROR('Boss Arena'!$J$10),ISERROR('Boss Arena'!$J$11),ISERROR('Boss Arena'!$J$12),ISERROR('Boss Arena'!$J$13),ISERROR('Boss Arena'!$J$14),ISERROR('Boss Arena'!$J$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$6),'Boss Arena'!$J$6=Key!$E$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$7),'Boss Arena'!$J$7=Key!$F$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$8),'Boss Arena'!$J$8=Key!$G$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$9),'Boss Arena'!$J$9=Key!$H$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$10),'Boss Arena'!$J$10=Key!$I$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$11),'Boss Arena'!$J$11=Key!$J$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$12),'Boss Arena'!$J$12=Key!$K$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$13),'Boss Arena'!$J$13=Key!$L$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$14),'Boss Arena'!$J$14=Key!$M$112),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$J$15),'Boss Arena'!$J$15=Key!$N$112),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6)))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF/IFS and AND"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E30" s="22"/>
@@ -5169,14 +5193,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="B31" s="31" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In L6 return TRUE when Ava (row 6) is NOT licensed (E6 is not ""Yes""). Use NOT.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$L$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$L$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$L$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$L$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('Boss Arena'!$L$6),'Boss Arena'!$L$6=(Key!$C$113="TRUE")),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"NOT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$L$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use NOT"))))),"LOCKED")</f>
@@ -5194,14 +5218,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="B32" s="31" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In E21 divide Total by Units with an IFERROR shield (0 on errors). Fill down to E26.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$E$21,'Boss Arena'!$E$22,'Boss Arena'!$E$23,'Boss Arena'!$E$24,'Boss Arena'!$E$25,'Boss Arena'!$E$26)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$E$21)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$22)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$23)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$24)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$25)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$26))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$E$21),ISERROR('Boss Arena'!$E$22),ISERROR('Boss Arena'!$E$23),ISERROR('Boss Arena'!$E$24),ISERROR('Boss Arena'!$E$25),ISERROR('Boss Arena'!$E$26)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$E$21),ABS('Boss Arena'!$E$21-Key!$E$114)&lt;=1E-9*MAX(1,ABS(Key!$E$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$22),ABS('Boss Arena'!$E$22-Key!$F$114)&lt;=1E-9*MAX(1,ABS(Key!$F$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$23),ABS('Boss Arena'!$E$23-Key!$G$114)&lt;=1E-9*MAX(1,ABS(Key!$G$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$24),ABS('Boss Arena'!$E$24-Key!$H$114)&lt;=1E-9*MAX(1,ABS(Key!$H$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$25),ABS('Boss Arena'!$E$25-Key!$I$114)&lt;=1E-9*MAX(1,ABS(Key!$I$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$26),ABS('Boss Arena'!$E$26-Key!$J$114)&lt;=1E-9*MAX(1,ABS(Key!$J$114))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFERROR"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$E$21)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFERROR"))))),"LOCKED")</f>
@@ -5219,14 +5243,14 @@
     </row>
     <row r="33" spans="1:7" ht="51.25" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="B33" s="31" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In H21 show ""Missing"" when the Name (G21) is empty, otherwise ""OK"" (use ISBLANK). Fill down to H25.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$H$21,'Boss Arena'!$H$22,'Boss Arena'!$H$23,'Boss Arena'!$H$24,'Boss Arena'!$H$25)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$H$21)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$22)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$23)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$24)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$25))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$H$21),ISERROR('Boss Arena'!$H$22),ISERROR('Boss Arena'!$H$23),ISERROR('Boss Arena'!$H$24),ISERROR('Boss Arena'!$H$25)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$H$21),'Boss Arena'!$H$21=Key!$E$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$22),'Boss Arena'!$H$22=Key!$F$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$23),'Boss Arena'!$H$23=Key!$G$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$24),'Boss Arena'!$H$24=Key!$H$115),FALSE),IFERROR(AND(ISTEXT('Boss Arena'!$H$25),'Boss Arena'!$H$25=Key!$I$115),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ISBLANK"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$H$21)))))),"✔ CLEAR","✘ CLOSE · right value, but use ISBLANK"))))),"LOCKED")</f>
@@ -5346,7 +5370,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -5359,10 +5383,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -5379,22 +5403,22 @@
         <v>12</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -5590,27 +5614,27 @@
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="27" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="G20" s="27" t="s">
         <v>9</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="5" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C21" s="5">
         <v>120</v>
@@ -5626,7 +5650,7 @@
     </row>
     <row r="22" spans="2:8">
       <c r="B22" s="5" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C22" s="5">
         <v>90</v>
@@ -5639,7 +5663,7 @@
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="5" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C23" s="5">
         <v>60</v>
@@ -5655,7 +5679,7 @@
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="5" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C24" s="5">
         <v>0</v>
@@ -5668,7 +5692,7 @@
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="5" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C25" s="5">
         <v>45</v>
@@ -5684,7 +5708,7 @@
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="5" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C26" s="5">
         <v>30</v>
@@ -5719,7 +5743,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5727,245 +5751,245 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>124</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.75" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.75" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>113</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.75" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>
@@ -6234,7 +6258,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>133</v>
       </c>
@@ -6253,46 +6277,55 @@
       <c r="H17" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" t="s">
+        <v>139</v>
+      </c>
+      <c r="K17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B18" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C18" cm="1" t="str">
         <f t="array" ref="C18">IF('F2-1 Arena'!$C$6&gt;=50,"TRUE","FALSE")</f>
         <v>TRUE</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C19" cm="1" t="str">
         <f t="array" ref="C19">IF('F2-1 Arena'!$E$7&lt;&gt;"No","TRUE","FALSE")</f>
         <v>TRUE</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C20" cm="1" t="str">
         <f t="array" ref="C20">IF('F2-1 Arena'!$E$8="yes","TRUE","FALSE")</f>
         <v>TRUE</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B21" t="s">
         <v>112</v>
@@ -6301,9 +6334,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B22" t="s">
         <v>117</v>
@@ -6312,9 +6345,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B23" t="s">
         <v>123</v>
@@ -6331,116 +6364,125 @@
       <c r="H23" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" t="s">
+        <v>138</v>
+      </c>
+      <c r="J23" t="s">
+        <v>139</v>
+      </c>
+      <c r="K23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E24" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B25" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E25" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E26" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B27" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E27" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F27" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E28" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B29" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E29" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B30" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B31" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C31" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E31" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F31" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G31" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H31" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B32" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C32" t="s">
         <v>118</v>
@@ -6460,10 +6502,10 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B33" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C33" t="s">
         <v>124</v>
@@ -6483,47 +6525,47 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E34" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F34" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G34" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H34" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I34" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J34" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B35" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E35" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B36" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E36" t="s">
         <v>124</v>
@@ -6531,10 +6573,10 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E37" cm="1" t="str">
         <f t="array" ref="E37">IF('F2-2 Arena'!$C$6&gt;=50,"Pass","Fail")</f>
@@ -6579,10 +6621,10 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B38" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E38" cm="1">
         <f t="array" ref="E38">IF('F2-2 Arena'!$C$6&gt;=80,'F2-2 Arena'!$C$6*10,0)</f>
@@ -6627,10 +6669,10 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B39" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C39" cm="1" t="str">
         <f t="array" ref="C39">IF('F2-2 Arena'!$J$6="","",'F2-2 Arena'!$J$6*2)</f>
@@ -6639,47 +6681,47 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E40" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F40" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G40" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H40" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I40" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J40" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B41" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E41" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B42" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E42" t="s">
         <v>124</v>
@@ -6687,261 +6729,261 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B43" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E43" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F43" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B44" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E44" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F44" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G44" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H44" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I44" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J44" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K44" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B45" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E45" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B46" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E46" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B47" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E47" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F47" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B48" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E48" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F48" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B49" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E49" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B50" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C50" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E50" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F50" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G50" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H50" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
+        <v>300</v>
+      </c>
+      <c r="B51" t="s">
+        <v>301</v>
+      </c>
+      <c r="C51" t="s">
+        <v>250</v>
+      </c>
+      <c r="E51" t="s">
+        <v>250</v>
+      </c>
+      <c r="F51" t="s">
         <v>297</v>
       </c>
-      <c r="B51" t="s">
-        <v>298</v>
-      </c>
-      <c r="C51" t="s">
-        <v>247</v>
-      </c>
-      <c r="E51" t="s">
-        <v>247</v>
-      </c>
-      <c r="F51" t="s">
-        <v>294</v>
-      </c>
       <c r="G51" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H51" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B52" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C52" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E52" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F52" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G52" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H52" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B53" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E53" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F53" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G53" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H53" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J53" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B54" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E54" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F54" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G54" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H54" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I54" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J54" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B55" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G55" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H55" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I55" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J55" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B56" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E56" cm="1" t="str">
         <f t="array" ref="E56">IF(AND('F2-3 Arena'!$D$6&gt;=18,'F2-3 Arena'!$E$6="Yes"),"Yes","No")</f>
@@ -6986,10 +7028,10 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B57" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E57" cm="1" t="str">
         <f t="array" ref="E57">IF(OR('F2-3 Arena'!$C$6&gt;=90,'F2-3 Arena'!$D$6&lt;16),"Prize","No prize")</f>
@@ -7034,10 +7076,10 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B58" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C58" cm="1" t="str">
         <f t="array" ref="C58">IF(NOT('F2-3 Arena'!$E$6="Yes"),"TRUE","FALSE")</f>
@@ -7046,207 +7088,207 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B59" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E59" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F59" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G59" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H59" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I59" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J59" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E60" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F60" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G60" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H60" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I60" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J60" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B61" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E61" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F61" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G61" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H61" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I61" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J61" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B62" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E62" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B63" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E63" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F63" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G63" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B64" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E64" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F64" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G64" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H64" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B65" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E65" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F65" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B66" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E66" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B67" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E67" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F67" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G67" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H67" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B68" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E68" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F68" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G68" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="H68" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I68" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="J68" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B69" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C69" t="s">
         <v>119</v>
@@ -7266,33 +7308,33 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B70" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C70" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E70" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F70" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G70" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H70" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B71" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C71" t="s">
         <v>113</v>
@@ -7312,61 +7354,76 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B72" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E72" t="s">
         <v>35</v>
       </c>
       <c r="F72" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B73" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E73" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F73" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G73" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H73" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I73" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="J73" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B74" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E74" t="s">
-        <v>411</v>
+        <v>414</v>
+      </c>
+      <c r="F74" t="s">
+        <v>415</v>
+      </c>
+      <c r="G74" t="s">
+        <v>416</v>
+      </c>
+      <c r="H74" t="s">
+        <v>417</v>
+      </c>
+      <c r="I74" t="s">
+        <v>418</v>
+      </c>
+      <c r="J74" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B75" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E75" cm="1" t="str">
         <f t="array" ref="E75">IF('F2-4 Arena'!$C$6&gt;=90,"A",IF('F2-4 Arena'!$C$6&gt;=75,"B","C"))</f>
@@ -7411,10 +7468,10 @@
     </row>
     <row r="76" spans="1:14">
       <c r="A76" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B76" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="E76" cm="1" t="str">
         <f t="array" ref="E76">_xlfn.IFS('F2-4 Arena'!$C$6&gt;=90,"Gold",'F2-4 Arena'!$C$6&gt;=75,"Silver",'F2-4 Arena'!$C$6&gt;=60,"Bronze",TRUE,"None")</f>
@@ -7459,69 +7516,84 @@
     </row>
     <row r="77" spans="1:14">
       <c r="A77" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B77" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C77" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E78" t="s">
         <v>35</v>
       </c>
       <c r="F78" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B79" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E79" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F79" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G79" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H79" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I79" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="J79" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B80" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E80" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+        <v>414</v>
+      </c>
+      <c r="F80" t="s">
+        <v>415</v>
+      </c>
+      <c r="G80" t="s">
+        <v>416</v>
+      </c>
+      <c r="H80" t="s">
+        <v>417</v>
+      </c>
+      <c r="I80" t="s">
+        <v>418</v>
+      </c>
+      <c r="J80" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="B81" t="s">
         <v>112</v>
@@ -7530,9 +7602,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B82" t="s">
         <v>117</v>
@@ -7541,9 +7613,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B83" t="s">
         <v>123</v>
@@ -7560,313 +7632,322 @@
       <c r="H83" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="84" spans="1:10">
+      <c r="I83" t="s">
+        <v>138</v>
+      </c>
+      <c r="J83" t="s">
+        <v>139</v>
+      </c>
+      <c r="K83" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B84" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E84" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="F84" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="G84" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="H84" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="I84" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="J84" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B85" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="E85" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F85" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="G85" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="H85" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="I85" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="J85" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E86" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="F86" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="G86" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="H86" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="I86" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="J86" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B87" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="E87" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="F87" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="G87" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="H87" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="I87" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="J87" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B88" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C88" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E88" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="F88" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G88" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H88" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="B89" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C89" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E89" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="F89" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G89" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H89" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B90" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C90" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E90" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F90" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G90" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H90" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
       <c r="A91" t="s">
+        <v>514</v>
+      </c>
+      <c r="B91" t="s">
+        <v>515</v>
+      </c>
+      <c r="C91" t="s">
+        <v>459</v>
+      </c>
+      <c r="E91" t="s">
+        <v>250</v>
+      </c>
+      <c r="F91" t="s">
+        <v>207</v>
+      </c>
+      <c r="G91" t="s">
+        <v>459</v>
+      </c>
+      <c r="H91" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" t="s">
+        <v>519</v>
+      </c>
+      <c r="B92" t="s">
         <v>506</v>
       </c>
-      <c r="B91" t="s">
-        <v>507</v>
-      </c>
-      <c r="C91" t="s">
-        <v>451</v>
-      </c>
-      <c r="E91" t="s">
-        <v>247</v>
-      </c>
-      <c r="F91" t="s">
-        <v>204</v>
-      </c>
-      <c r="G91" t="s">
-        <v>451</v>
-      </c>
-      <c r="H91" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
-      <c r="A92" t="s">
-        <v>511</v>
-      </c>
-      <c r="B92" t="s">
-        <v>498</v>
-      </c>
       <c r="E92" t="s">
+        <v>520</v>
+      </c>
+      <c r="F92" t="s">
+        <v>521</v>
+      </c>
+      <c r="G92" t="s">
+        <v>522</v>
+      </c>
+      <c r="H92" t="s">
+        <v>454</v>
+      </c>
+      <c r="I92" t="s">
+        <v>523</v>
+      </c>
+      <c r="J92" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" t="s">
+        <v>525</v>
+      </c>
+      <c r="B93" t="s">
+        <v>509</v>
+      </c>
+      <c r="E93" t="s">
+        <v>526</v>
+      </c>
+      <c r="F93" t="s">
+        <v>527</v>
+      </c>
+      <c r="G93" t="s">
+        <v>528</v>
+      </c>
+      <c r="H93" t="s">
+        <v>297</v>
+      </c>
+      <c r="I93" t="s">
+        <v>529</v>
+      </c>
+      <c r="J93" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" t="s">
+        <v>531</v>
+      </c>
+      <c r="B94" t="s">
         <v>512</v>
       </c>
-      <c r="F92" t="s">
-        <v>513</v>
-      </c>
-      <c r="G92" t="s">
-        <v>514</v>
-      </c>
-      <c r="H92" t="s">
-        <v>446</v>
-      </c>
-      <c r="I92" t="s">
+      <c r="E94" t="s">
+        <v>532</v>
+      </c>
+      <c r="F94" t="s">
+        <v>533</v>
+      </c>
+      <c r="G94" t="s">
+        <v>534</v>
+      </c>
+      <c r="H94" t="s">
+        <v>208</v>
+      </c>
+      <c r="I94" t="s">
+        <v>535</v>
+      </c>
+      <c r="J94" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" t="s">
+        <v>537</v>
+      </c>
+      <c r="B95" t="s">
         <v>515</v>
       </c>
-      <c r="J92" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="A93" t="s">
-        <v>517</v>
-      </c>
-      <c r="B93" t="s">
-        <v>501</v>
-      </c>
-      <c r="E93" t="s">
-        <v>518</v>
-      </c>
-      <c r="F93" t="s">
-        <v>519</v>
-      </c>
-      <c r="G93" t="s">
-        <v>520</v>
-      </c>
-      <c r="H93" t="s">
-        <v>294</v>
-      </c>
-      <c r="I93" t="s">
-        <v>521</v>
-      </c>
-      <c r="J93" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
-      <c r="A94" t="s">
-        <v>523</v>
-      </c>
-      <c r="B94" t="s">
-        <v>504</v>
-      </c>
-      <c r="E94" t="s">
-        <v>524</v>
-      </c>
-      <c r="F94" t="s">
-        <v>525</v>
-      </c>
-      <c r="G94" t="s">
-        <v>526</v>
-      </c>
-      <c r="H94" t="s">
-        <v>205</v>
-      </c>
-      <c r="I94" t="s">
-        <v>527</v>
-      </c>
-      <c r="J94" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
-      <c r="A95" t="s">
-        <v>529</v>
-      </c>
-      <c r="B95" t="s">
-        <v>507</v>
-      </c>
       <c r="E95" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="F95" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="G95" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="H95" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="I95" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="J95" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="B96" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="E96" cm="1">
         <f t="array" ref="E96">IFERROR('F2-5 Arena'!$C$6/'F2-5 Arena'!$D$6,0)</f>
@@ -7895,10 +7976,10 @@
     </row>
     <row r="97" spans="1:14">
       <c r="A97" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B97" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C97" cm="1" t="str">
         <f t="array" ref="C97">_xlfn.IFNA('F2-5 Arena'!$D$14,"Missing")</f>
@@ -7907,10 +7988,10 @@
     </row>
     <row r="98" spans="1:14">
       <c r="A98" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B98" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="E98" cm="1" t="str">
         <f t="array" ref="E98">IF(ISBLANK('F2-5 Arena'!$B$17),"Missing","OK")</f>
@@ -7935,10 +8016,10 @@
     </row>
     <row r="99" spans="1:14">
       <c r="A99" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B99" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="E99" cm="1" t="str">
         <f t="array" ref="E99">IF(ISNUMBER('F2-5 Arena'!$D$23),"Number","Text")</f>
@@ -7963,151 +8044,151 @@
     </row>
     <row r="100" spans="1:14">
       <c r="A100" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B100" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="E100" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="F100" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="G100" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="H100" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="I100" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="J100" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B101" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="E101" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F101" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="G101" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="H101" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I101" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="J101" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B102" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E102" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="F102" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="G102" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="H102" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I102" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="J102" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B103" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="E103" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="F103" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="G103" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="H103" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="I103" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="J103" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="B104" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E104" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F104" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G104" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H104" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I104" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J104" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="B105" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E105" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E106" t="s">
         <v>124</v>
@@ -8115,36 +8196,36 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B107" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="E107" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="F107" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="G107" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="H107" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="I107" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="J107" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="B108" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="E108" cm="1" t="str">
         <f t="array" ref="E108">IF('Boss Arena'!$C$6&gt;=60,"Pass","Fail")</f>
@@ -8189,10 +8270,10 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="B109" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="E109" cm="1" t="str">
         <f t="array" ref="E109">IF(AND('Boss Arena'!$D$6&gt;=18,'Boss Arena'!$C$6&gt;=70),"Yes","No")</f>
@@ -8237,10 +8318,10 @@
     </row>
     <row r="110" spans="1:14">
       <c r="A110" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="B110" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="E110" cm="1" t="str">
         <f t="array" ref="E110">IF(OR('Boss Arena'!$C$6&gt;=95,'Boss Arena'!$D$6&gt;=40),"Star","No")</f>
@@ -8285,10 +8366,10 @@
     </row>
     <row r="111" spans="1:14">
       <c r="A111" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="B111" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="E111" cm="1" t="str">
         <f t="array" ref="E111">_xlfn.IFS('Boss Arena'!$C$6&gt;=90,"Gold",'Boss Arena'!$C$6&gt;=75,"Silver",'Boss Arena'!$C$6&gt;=60,"Bronze",TRUE,"None")</f>
@@ -8333,10 +8414,10 @@
     </row>
     <row r="112" spans="1:14">
       <c r="A112" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="B112" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="E112" cm="1" t="str">
         <f t="array" ref="E112">IF(AND('Boss Arena'!$C$6&gt;=80,'Boss Arena'!$D$6&gt;=18),"VIP",IF('Boss Arena'!$C$6&gt;=60,"Member","Guest"))</f>
@@ -8381,10 +8462,10 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="B113" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="C113" cm="1" t="str">
         <f t="array" ref="C113">IF(NOT('Boss Arena'!$E$6="Yes"),"TRUE","FALSE")</f>
@@ -8393,10 +8474,10 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="B114" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="E114" cm="1">
         <f t="array" ref="E114">IFERROR('Boss Arena'!$C$21/'Boss Arena'!$D$21,0)</f>
@@ -8425,10 +8506,10 @@
     </row>
     <row r="115" spans="1:10">
       <c r="A115" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="B115" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="E115" cm="1" t="str">
         <f t="array" ref="E115">IF(ISBLANK('Boss Arena'!$G$21),"Missing","OK")</f>
@@ -8476,7 +8557,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8487,7 +8568,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9006,14 +9087,14 @@
     </row>
     <row r="35" spans="1:7" ht="19.75" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
-        <f t="array" ref="D35">IFERROR(_xlfn.LET(_xlpm.a,'F2-1 True or False'!$C$35,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$17:$H$17),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D35">IFERROR(_xlfn.LET(_xlpm.a,'F2-1 True or False'!$C$35,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$17:$K$17),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E35" s="22"/>
@@ -9028,13 +9109,13 @@
     </row>
     <row r="36" spans="1:7" ht="51.25" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F2-1 Arena'!$G$6),"",IF(NOT(_xlfn.ISFORMULA('F2-1 Arena'!$G$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-1 Arena'!$G$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-1 Arena'!$G$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('F2-1 Arena'!$G$6),'F2-1 Arena'!$G$6=(Key!$C$18="TRUE")),FALSE))),"✘ TRY AGAIN","✔ CLEAR"))))</f>
@@ -9052,13 +9133,13 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F2-1 Arena'!$G$7),"",IF(NOT(_xlfn.ISFORMULA('F2-1 Arena'!$G$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-1 Arena'!$G$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-1 Arena'!$G$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('F2-1 Arena'!$G$7),'F2-1 Arena'!$G$7=(Key!$C$19="TRUE")),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("&lt;&gt;",_xlfn.FORMULATEXT('F2-1 Arena'!$G$7))),"✔ CLEAR","✘ CLOSE · your formula needs &lt;&gt;")))))</f>
@@ -9076,13 +9157,13 @@
     </row>
     <row r="38" spans="1:7" ht="51.25" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F2-1 Arena'!$G$8),"",IF(NOT(_xlfn.ISFORMULA('F2-1 Arena'!$G$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-1 Arena'!$G$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-1 Arena'!$G$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('F2-1 Arena'!$G$8),'F2-1 Arena'!$G$8=(Key!$C$20="TRUE")),FALSE))),"✘ TRY AGAIN","✔ CLEAR"))))</f>
@@ -9429,7 +9510,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9440,7 +9521,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9492,10 +9573,10 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="67" customHeight="1">
@@ -9503,7 +9584,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>118</v>
@@ -9514,7 +9595,7 @@
         <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>124</v>
@@ -9559,7 +9640,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -9581,7 +9662,7 @@
         <v>55</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -9603,11 +9684,11 @@
         <v>60</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
-        <f t="array" ref="D15">IFERROR(_xlfn.LET(_xlpm.a,'F2-2 Fork in the Road'!$C$15,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$23:$H$23),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D15">IFERROR(_xlfn.LET(_xlpm.a,'F2-2 Fork in the Road'!$C$15,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$23:$K$23),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E15" s="22"/>
@@ -9625,7 +9706,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -9647,7 +9728,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -9669,7 +9750,7 @@
         <v>75</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -9691,7 +9772,7 @@
         <v>80</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -9713,7 +9794,7 @@
         <v>85</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -9735,7 +9816,7 @@
         <v>94</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -9757,7 +9838,7 @@
         <v>108</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -9813,7 +9894,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -9835,7 +9916,7 @@
         <v>120</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -9857,7 +9938,7 @@
         <v>125</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -9887,7 +9968,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -9918,7 +9999,7 @@
         <v>130</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -9940,7 +10021,7 @@
         <v>132</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -9959,10 +10040,10 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -9981,13 +10062,13 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(COUNTA('F2-2 Arena'!$F$6,'F2-2 Arena'!$F$7,'F2-2 Arena'!$F$8,'F2-2 Arena'!$F$9,'F2-2 Arena'!$F$10,'F2-2 Arena'!$F$11,'F2-2 Arena'!$F$12,'F2-2 Arena'!$F$13,'F2-2 Arena'!$F$14,'F2-2 Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$6)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$7)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$8)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$9)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$10)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$11)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$12)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$13)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$14)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-2 Arena'!$F$6),ISERROR('F2-2 Arena'!$F$7),ISERROR('F2-2 Arena'!$F$8),ISERROR('F2-2 Arena'!$F$9),ISERROR('F2-2 Arena'!$F$10),ISERROR('F2-2 Arena'!$F$11),ISERROR('F2-2 Arena'!$F$12),ISERROR('F2-2 Arena'!$F$13),ISERROR('F2-2 Arena'!$F$14),ISERROR('F2-2 Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-2 Arena'!$F$6),'F2-2 Arena'!$F$6=Key!$E$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$7),'F2-2 Arena'!$F$7=Key!$F$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$8),'F2-2 Arena'!$F$8=Key!$G$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$9),'F2-2 Arena'!$F$9=Key!$H$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$10),'F2-2 Arena'!$F$10=Key!$I$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$11),'F2-2 Arena'!$F$11=Key!$J$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$12),'F2-2 Arena'!$F$12=Key!$K$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$13),'F2-2 Arena'!$F$13=Key!$L$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$14),'F2-2 Arena'!$F$14=Key!$M$37),FALSE),IFERROR(AND(ISTEXT('F2-2 Arena'!$F$15),'F2-2 Arena'!$F$15=Key!$N$37),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-2 Arena'!$F$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF")))))</f>
@@ -10005,13 +10086,13 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(COUNTA('F2-2 Arena'!$G$6,'F2-2 Arena'!$G$7,'F2-2 Arena'!$G$8,'F2-2 Arena'!$G$9,'F2-2 Arena'!$G$10,'F2-2 Arena'!$G$11,'F2-2 Arena'!$G$12,'F2-2 Arena'!$G$13,'F2-2 Arena'!$G$14,'F2-2 Arena'!$G$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$6)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$7)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$8)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$9)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$10)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$11)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$12)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$13)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$14)),NOT(_xlfn.ISFORMULA('F2-2 Arena'!$G$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-2 Arena'!$G$6),ISERROR('F2-2 Arena'!$G$7),ISERROR('F2-2 Arena'!$G$8),ISERROR('F2-2 Arena'!$G$9),ISERROR('F2-2 Arena'!$G$10),ISERROR('F2-2 Arena'!$G$11),ISERROR('F2-2 Arena'!$G$12),ISERROR('F2-2 Arena'!$G$13),ISERROR('F2-2 Arena'!$G$14),ISERROR('F2-2 Arena'!$G$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$6),ABS('F2-2 Arena'!$G$6-Key!$E$38)&lt;=1E-9*MAX(1,ABS(Key!$E$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$7),ABS('F2-2 Arena'!$G$7-Key!$F$38)&lt;=1E-9*MAX(1,ABS(Key!$F$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$8),ABS('F2-2 Arena'!$G$8-Key!$G$38)&lt;=1E-9*MAX(1,ABS(Key!$G$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$9),ABS('F2-2 Arena'!$G$9-Key!$H$38)&lt;=1E-9*MAX(1,ABS(Key!$H$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$10),ABS('F2-2 Arena'!$G$10-Key!$I$38)&lt;=1E-9*MAX(1,ABS(Key!$I$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$11),ABS('F2-2 Arena'!$G$11-Key!$J$38)&lt;=1E-9*MAX(1,ABS(Key!$J$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$12),ABS('F2-2 Arena'!$G$12-Key!$K$38)&lt;=1E-9*MAX(1,ABS(Key!$K$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$13),ABS('F2-2 Arena'!$G$13-Key!$L$38)&lt;=1E-9*MAX(1,ABS(Key!$L$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$14),ABS('F2-2 Arena'!$G$14-Key!$M$38)&lt;=1E-9*MAX(1,ABS(Key!$M$38))),FALSE),IFERROR(AND(ISNUMBER('F2-2 Arena'!$G$15),ABS('F2-2 Arena'!$G$15-Key!$N$38)&lt;=1E-9*MAX(1,ABS(Key!$N$38))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-2 Arena'!$G$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF")))))</f>
@@ -10029,16 +10110,16 @@
     </row>
     <row r="38" spans="1:7" ht="51.25" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
-        <f t="array" ref="D38">IF(ISBLANK('F2-2 Arena'!$I$6),"",IF(NOT(_xlfn.ISFORMULA('F2-2 Arena'!$I$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-2 Arena'!$I$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-2 Arena'!$I$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F2-2 Arena'!$I$6),'F2-2 Arena'!$I$6=Key!$C$39),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-2 Arena'!$I$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF")))))</f>
+        <f t="array" ref="D38">IF(ISBLANK('F2-2 Arena'!$I$6),"",IF(NOT(_xlfn.ISFORMULA('F2-2 Arena'!$I$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-2 Arena'!$I$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-2 Arena'!$I$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F2-2 Arena'!$I$6),'F2-2 Arena'!$I$6=Key!$C$39),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-2 Arena'!$I$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-2 Arena'!$I$6))))))),"✔ CLEAR","✘ CLOSE · right value, but use IF/IFS")))))</f>
         <v/>
       </c>
       <c r="E38" s="22"/>
@@ -10169,7 +10250,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -10182,10 +10263,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -10205,13 +10286,13 @@
         <v>44</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -10403,7 +10484,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10414,7 +10495,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -10466,10 +10547,10 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="35.5" customHeight="1">
@@ -10477,10 +10558,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.5" customHeight="1">
@@ -10488,10 +10569,10 @@
         <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1">
@@ -10533,7 +10614,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -10555,7 +10636,7 @@
         <v>55</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -10577,7 +10658,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -10599,7 +10680,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -10621,7 +10702,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -10643,7 +10724,7 @@
         <v>75</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -10665,7 +10746,7 @@
         <v>80</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -10687,7 +10768,7 @@
         <v>85</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -10709,7 +10790,7 @@
         <v>94</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -10731,7 +10812,7 @@
         <v>108</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -10787,7 +10868,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -10809,7 +10890,7 @@
         <v>120</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -10831,7 +10912,7 @@
         <v>125</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -10861,7 +10942,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -10892,7 +10973,7 @@
         <v>130</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -10914,7 +10995,7 @@
         <v>132</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -10933,10 +11014,10 @@
     </row>
     <row r="35" spans="1:7" ht="19.75" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -10955,13 +11036,13 @@
     </row>
     <row r="36" spans="1:7" ht="51.25" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(COUNTA('F2-3 Arena'!$F$6,'F2-3 Arena'!$F$7,'F2-3 Arena'!$F$8,'F2-3 Arena'!$F$9,'F2-3 Arena'!$F$10,'F2-3 Arena'!$F$11,'F2-3 Arena'!$F$12,'F2-3 Arena'!$F$13,'F2-3 Arena'!$F$14,'F2-3 Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$6)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$7)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$8)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$9)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$10)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$11)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$12)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$13)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$14)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-3 Arena'!$F$6),ISERROR('F2-3 Arena'!$F$7),ISERROR('F2-3 Arena'!$F$8),ISERROR('F2-3 Arena'!$F$9),ISERROR('F2-3 Arena'!$F$10),ISERROR('F2-3 Arena'!$F$11),ISERROR('F2-3 Arena'!$F$12),ISERROR('F2-3 Arena'!$F$13),ISERROR('F2-3 Arena'!$F$14),ISERROR('F2-3 Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-3 Arena'!$F$6),'F2-3 Arena'!$F$6=Key!$E$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$7),'F2-3 Arena'!$F$7=Key!$F$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$8),'F2-3 Arena'!$F$8=Key!$G$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$9),'F2-3 Arena'!$F$9=Key!$H$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$10),'F2-3 Arena'!$F$10=Key!$I$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$11),'F2-3 Arena'!$F$11=Key!$J$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$12),'F2-3 Arena'!$F$12=Key!$K$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$13),'F2-3 Arena'!$F$13=Key!$L$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$14),'F2-3 Arena'!$F$14=Key!$M$56),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$F$15),'F2-3 Arena'!$F$15=Key!$N$56),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-3 Arena'!$F$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use AND")))))</f>
@@ -10979,13 +11060,13 @@
     </row>
     <row r="37" spans="1:7" ht="51.25" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(COUNTA('F2-3 Arena'!$G$6,'F2-3 Arena'!$G$7,'F2-3 Arena'!$G$8,'F2-3 Arena'!$G$9,'F2-3 Arena'!$G$10,'F2-3 Arena'!$G$11,'F2-3 Arena'!$G$12,'F2-3 Arena'!$G$13,'F2-3 Arena'!$G$14,'F2-3 Arena'!$G$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$6)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$7)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$8)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$9)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$10)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$11)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$12)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$13)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$14)),NOT(_xlfn.ISFORMULA('F2-3 Arena'!$G$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-3 Arena'!$G$6),ISERROR('F2-3 Arena'!$G$7),ISERROR('F2-3 Arena'!$G$8),ISERROR('F2-3 Arena'!$G$9),ISERROR('F2-3 Arena'!$G$10),ISERROR('F2-3 Arena'!$G$11),ISERROR('F2-3 Arena'!$G$12),ISERROR('F2-3 Arena'!$G$13),ISERROR('F2-3 Arena'!$G$14),ISERROR('F2-3 Arena'!$G$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-3 Arena'!$G$6),'F2-3 Arena'!$G$6=Key!$E$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$7),'F2-3 Arena'!$G$7=Key!$F$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$8),'F2-3 Arena'!$G$8=Key!$G$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$9),'F2-3 Arena'!$G$9=Key!$H$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$10),'F2-3 Arena'!$G$10=Key!$I$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$11),'F2-3 Arena'!$G$11=Key!$J$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$12),'F2-3 Arena'!$G$12=Key!$K$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$13),'F2-3 Arena'!$G$13=Key!$L$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$14),'F2-3 Arena'!$G$14=Key!$M$57),FALSE),IFERROR(AND(ISTEXT('F2-3 Arena'!$G$15),'F2-3 Arena'!$G$15=Key!$N$57),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"OR"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-3 Arena'!$G$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use OR")))))</f>
@@ -11003,13 +11084,13 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F2-3 Arena'!$I$6),"",IF(NOT(_xlfn.ISFORMULA('F2-3 Arena'!$I$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F2-3 Arena'!$I$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F2-3 Arena'!$I$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISLOGICAL('F2-3 Arena'!$I$6),'F2-3 Arena'!$I$6=(Key!$C$58="TRUE")),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"NOT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-3 Arena'!$I$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use NOT")))))</f>
@@ -11143,7 +11224,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -11156,10 +11237,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -11176,13 +11257,13 @@
         <v>12</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -11374,7 +11455,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11385,7 +11466,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -11437,7 +11518,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>119</v>
@@ -11448,10 +11529,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="51.25" customHeight="1">
@@ -11459,7 +11540,7 @@
         <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>113</v>
@@ -11504,7 +11585,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -11526,7 +11607,7 @@
         <v>55</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -11548,7 +11629,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -11570,7 +11651,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -11592,7 +11673,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -11614,7 +11695,7 @@
         <v>75</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -11636,7 +11717,7 @@
         <v>80</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -11658,7 +11739,7 @@
         <v>85</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -11680,7 +11761,7 @@
         <v>94</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -11702,7 +11783,7 @@
         <v>108</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -11758,7 +11839,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -11780,7 +11861,7 @@
         <v>120</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -11802,7 +11883,7 @@
         <v>125</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -11832,7 +11913,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -11863,7 +11944,7 @@
         <v>130</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -11885,7 +11966,7 @@
         <v>132</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -11904,14 +11985,14 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
-        <f t="array" ref="D35">IFERROR(_xlfn.LET(_xlpm.a,'F2-4 Multi-Level'!$C$35,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$74:$E$74),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D35">IFERROR(_xlfn.LET(_xlpm.a,'F2-4 Multi-Level'!$C$35,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$74:$J$74),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E35" s="22"/>
@@ -11926,13 +12007,13 @@
     </row>
     <row r="36" spans="1:7" ht="51.25" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(COUNTA('F2-4 Arena'!$F$6,'F2-4 Arena'!$F$7,'F2-4 Arena'!$F$8,'F2-4 Arena'!$F$9,'F2-4 Arena'!$F$10,'F2-4 Arena'!$F$11,'F2-4 Arena'!$F$12,'F2-4 Arena'!$F$13,'F2-4 Arena'!$F$14,'F2-4 Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$6)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$7)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$8)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$9)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$10)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$11)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$12)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$13)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$14)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-4 Arena'!$F$6),ISERROR('F2-4 Arena'!$F$7),ISERROR('F2-4 Arena'!$F$8),ISERROR('F2-4 Arena'!$F$9),ISERROR('F2-4 Arena'!$F$10),ISERROR('F2-4 Arena'!$F$11),ISERROR('F2-4 Arena'!$F$12),ISERROR('F2-4 Arena'!$F$13),ISERROR('F2-4 Arena'!$F$14),ISERROR('F2-4 Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-4 Arena'!$F$6),'F2-4 Arena'!$F$6=Key!$E$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$7),'F2-4 Arena'!$F$7=Key!$F$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$8),'F2-4 Arena'!$F$8=Key!$G$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$9),'F2-4 Arena'!$F$9=Key!$H$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$10),'F2-4 Arena'!$F$10=Key!$I$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$11),'F2-4 Arena'!$F$11=Key!$J$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$12),'F2-4 Arena'!$F$12=Key!$K$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$13),'F2-4 Arena'!$F$13=Key!$L$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$14),'F2-4 Arena'!$F$14=Key!$M$75),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$F$15),'F2-4 Arena'!$F$15=Key!$N$75),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-4 Arena'!$F$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IF")))))</f>
@@ -11950,13 +12031,13 @@
     </row>
     <row r="37" spans="1:7" ht="51.25" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(COUNTA('F2-4 Arena'!$G$6,'F2-4 Arena'!$G$7,'F2-4 Arena'!$G$8,'F2-4 Arena'!$G$9,'F2-4 Arena'!$G$10,'F2-4 Arena'!$G$11,'F2-4 Arena'!$G$12,'F2-4 Arena'!$G$13,'F2-4 Arena'!$G$14,'F2-4 Arena'!$G$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$6)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$7)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$8)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$9)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$10)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$11)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$12)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$13)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$14)),NOT(_xlfn.ISFORMULA('F2-4 Arena'!$G$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F2-4 Arena'!$G$6),ISERROR('F2-4 Arena'!$G$7),ISERROR('F2-4 Arena'!$G$8),ISERROR('F2-4 Arena'!$G$9),ISERROR('F2-4 Arena'!$G$10),ISERROR('F2-4 Arena'!$G$11),ISERROR('F2-4 Arena'!$G$12),ISERROR('F2-4 Arena'!$G$13),ISERROR('F2-4 Arena'!$G$14),ISERROR('F2-4 Arena'!$G$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISTEXT('F2-4 Arena'!$G$6),'F2-4 Arena'!$G$6=Key!$E$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$7),'F2-4 Arena'!$G$7=Key!$F$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$8),'F2-4 Arena'!$G$8=Key!$G$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$9),'F2-4 Arena'!$G$9=Key!$H$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$10),'F2-4 Arena'!$G$10=Key!$I$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$11),'F2-4 Arena'!$G$11=Key!$J$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$12),'F2-4 Arena'!$G$12=Key!$K$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$13),'F2-4 Arena'!$G$13=Key!$L$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$14),'F2-4 Arena'!$G$14=Key!$M$76),FALSE),IFERROR(AND(ISTEXT('F2-4 Arena'!$G$15),'F2-4 Arena'!$G$15=Key!$N$76),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"IFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F2-4 Arena'!$G$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use IFS")))))</f>
@@ -11974,10 +12055,10 @@
     </row>
     <row r="38" spans="1:7" ht="51.25" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -12112,7 +12193,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -12125,10 +12206,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -12145,13 +12226,13 @@
         <v>12</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -12170,7 +12251,7 @@
       <c r="F6" s="28"/>
       <c r="G6" s="28"/>
       <c r="I6" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:9">
